--- a/config/template.xlsx
+++ b/config/template.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shawnpxf/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2FF51BE-8873-4A42-88B5-B1DB6BF00994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF98D1C-F4F0-FA4C-A366-0049FCD32FA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="28000" windowHeight="15060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="导入说明" sheetId="2" r:id="rId1"/>
-    <sheet name="餐品数据" sheetId="1" r:id="rId2"/>
+    <sheet name="导入说明" sheetId="1" r:id="rId1"/>
+    <sheet name="餐品数据" sheetId="2" r:id="rId2"/>
     <sheet name="标品数据" sheetId="3" r:id="rId3"/>
     <sheet name="套餐数据" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -32,9 +32,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商品的堂食会员价；
 2、外卖会员价、自提会员价、商城会员价未设置时以该价格执行；
@@ -46,9 +48,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>用于小程序端展示划线价；</t>
         </r>
@@ -58,9 +62,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>设置打包费金额，用于外卖、自提等业务收取打包费；</t>
         </r>
@@ -70,9 +76,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务指定价格；
 2、未设置时以售价执行</t>
@@ -83,9 +91,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">1、自提业务指定价格；
 2、未设置时以售价执行
@@ -97,9 +107,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务指定价格；
 2、未设置时以售价执行</t>
@@ -110,9 +122,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务的会员价格；
 2、未设置时以会员价执行；
@@ -124,9 +138,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、自提业务的会员价格；
 2、未设置时以会员价执行；
@@ -138,9 +154,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务的会员价格；
 2、未设置时以会员价执行；
@@ -152,9 +170,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商品的堂食会员价；
 2、外卖会员价、自提会员价、商城会员价未设置时以该价格执行；
@@ -166,9 +186,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>用于小程序端展示划线价；</t>
         </r>
@@ -178,9 +200,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>设置打包费金额，用于外卖、自提等业务收取打包费；</t>
         </r>
@@ -190,9 +214,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务指定价格；
 2、未设置时以售价执行</t>
@@ -203,9 +229,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">1、自提业务指定价格；
 2、未设置时以售价执行
@@ -217,9 +245,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务指定价格；
 2、未设置时以售价执行</t>
@@ -230,9 +260,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务的会员价格；
 2、未设置时以会员价执行；
@@ -244,9 +276,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、自提业务的会员价格；
 2、未设置时以会员价执行；
@@ -258,9 +292,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务的会员价格；
 2、未设置时以会员价执行；
@@ -272,9 +308,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商品的堂食会员价；
 2、外卖会员价、自提会员价、商城会员价未设置时以该价格执行；
@@ -286,9 +324,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>用于小程序端展示划线价；</t>
         </r>
@@ -298,9 +338,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>设置打包费金额，用于外卖、自提等业务收取打包费；</t>
         </r>
@@ -310,9 +352,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务指定价格；
 2、未设置时以售价执行</t>
@@ -323,9 +367,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">1、自提业务指定价格；
 2、未设置时以售价执行
@@ -337,9 +383,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务指定价格；
 2、未设置时以售价执行</t>
@@ -350,9 +398,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务的会员价格；
 2、未设置时以会员价执行；
@@ -364,9 +414,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、自提业务的会员价格；
 2、未设置时以会员价执行；
@@ -378,9 +430,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务的会员价格；
 2、未设置时以会员价执行；
@@ -392,9 +446,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商品的堂食会员价；
 2、外卖会员价、自提会员价、商城会员价未设置时以该价格执行；
@@ -406,9 +462,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>用于小程序端展示划线价；</t>
         </r>
@@ -418,9 +476,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>设置打包费金额，用于外卖、自提等业务收取打包费；</t>
         </r>
@@ -430,9 +490,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务指定价格；
 2、未设置时以售价执行</t>
@@ -443,9 +505,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">1、自提业务指定价格；
 2、未设置时以售价执行
@@ -457,9 +521,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务指定价格；
 2、未设置时以售价执行</t>
@@ -470,9 +536,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务的会员价格；
 2、未设置时以会员价执行；
@@ -484,9 +552,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、自提业务的会员价格；
 2、未设置时以会员价执行；
@@ -498,9 +568,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务的会员价格；
 2、未设置时以会员价执行；
@@ -512,9 +584,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商品的堂食会员价；
 2、外卖会员价、自提会员价、商城会员价未设置时以该价格执行；
@@ -526,9 +600,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>用于小程序端展示划线价；</t>
         </r>
@@ -538,9 +614,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>设置打包费金额，用于外卖、自提等业务收取打包费；</t>
         </r>
@@ -550,9 +628,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务指定价格；
 2、未设置时以售价执行</t>
@@ -563,9 +643,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">1、自提业务指定价格；
 2、未设置时以售价执行
@@ -577,9 +659,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务指定价格；
 2、未设置时以售价执行</t>
@@ -590,9 +674,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务的会员价格；
 2、未设置时以会员价执行；
@@ -604,9 +690,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、自提业务的会员价格；
 2、未设置时以会员价执行；
@@ -618,9 +706,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务的会员价格；
 2、未设置时以会员价执行；
@@ -632,9 +722,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商品的堂食会员价；
 2、外卖会员价、自提会员价、商城会员价未设置时以该价格执行；
@@ -646,9 +738,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>用于小程序端展示划线价；</t>
         </r>
@@ -658,9 +752,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>设置打包费金额，用于外卖、自提等业务收取打包费；</t>
         </r>
@@ -670,9 +766,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务指定价格；
 2、未设置时以售价执行</t>
@@ -683,9 +781,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">1、自提业务指定价格；
 2、未设置时以售价执行
@@ -697,9 +797,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务指定价格；
 2、未设置时以售价执行</t>
@@ -710,9 +812,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务的会员价格；
 2、未设置时以会员价执行；
@@ -724,9 +828,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、自提业务的会员价格；
 2、未设置时以会员价执行；
@@ -738,9 +844,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务的会员价格；
 2、未设置时以会员价执行；
@@ -752,9 +860,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商品的堂食会员价；
 2、外卖会员价、自提会员价、商城会员价未设置时以该价格执行；
@@ -766,9 +876,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>用于小程序端展示划线价；</t>
         </r>
@@ -778,9 +890,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>设置打包费金额，用于外卖、自提等业务收取打包费；</t>
         </r>
@@ -790,9 +904,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务指定价格；
 2、未设置时以售价执行</t>
@@ -803,9 +919,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">1、自提业务指定价格；
 2、未设置时以售价执行
@@ -817,9 +935,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务指定价格；
 2、未设置时以售价执行</t>
@@ -830,9 +950,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务的会员价格；
 2、未设置时以会员价执行；
@@ -844,9 +966,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、自提业务的会员价格；
 2、未设置时以会员价执行；
@@ -858,9 +982,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务的会员价格；
 2、未设置时以会员价执行；
@@ -872,9 +998,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商品的堂食会员价；
 2、外卖会员价、自提会员价、商城会员价未设置时以该价格执行；
@@ -886,9 +1014,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>用于小程序端展示划线价；</t>
         </r>
@@ -898,9 +1028,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>设置打包费金额，用于外卖、自提等业务收取打包费；</t>
         </r>
@@ -910,9 +1042,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务指定价格；
 2、未设置时以售价执行</t>
@@ -923,9 +1057,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">1、自提业务指定价格；
 2、未设置时以售价执行
@@ -937,9 +1073,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务指定价格；
 2、未设置时以售价执行</t>
@@ -950,9 +1088,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务的会员价格；
 2、未设置时以会员价执行；
@@ -964,9 +1104,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、自提业务的会员价格；
 2、未设置时以会员价执行；
@@ -978,9 +1120,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务的会员价格；
 2、未设置时以会员价执行；
@@ -992,9 +1136,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商品的堂食会员价；
 2、外卖会员价、自提会员价、商城会员价未设置时以该价格执行；
@@ -1006,9 +1152,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>用于小程序端展示划线价；</t>
         </r>
@@ -1018,9 +1166,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>设置打包费金额，用于外卖、自提等业务收取打包费；</t>
         </r>
@@ -1030,9 +1180,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务指定价格；
 2、未设置时以售价执行</t>
@@ -1043,9 +1195,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">1、自提业务指定价格；
 2、未设置时以售价执行
@@ -1057,9 +1211,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务指定价格；
 2、未设置时以售价执行</t>
@@ -1070,9 +1226,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务的会员价格；
 2、未设置时以会员价执行；
@@ -1084,9 +1242,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、自提业务的会员价格；
 2、未设置时以会员价执行；
@@ -1098,9 +1258,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务的会员价格；
 2、未设置时以会员价执行；
@@ -1112,9 +1274,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商品的堂食会员价；
 2、外卖会员价、自提会员价、商城会员价未设置时以该价格执行；
@@ -1126,9 +1290,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>用于小程序端展示划线价；</t>
         </r>
@@ -1138,9 +1304,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>设置打包费金额，用于外卖、自提等业务收取打包费；</t>
         </r>
@@ -1150,9 +1318,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务指定价格；
 2、未设置时以售价执行</t>
@@ -1163,9 +1333,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">1、自提业务指定价格；
 2、未设置时以售价执行
@@ -1177,9 +1349,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务指定价格；
 2、未设置时以售价执行</t>
@@ -1190,9 +1364,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务的会员价格；
 2、未设置时以会员价执行；
@@ -1204,9 +1380,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、自提业务的会员价格；
 2、未设置时以会员价执行；
@@ -1218,9 +1396,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务的会员价格；
 2、未设置时以会员价执行；
@@ -1242,9 +1422,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商品的堂食会员价；
 2、外卖会员价、自提会员价、商城会员价未设置时以该价格执行；
@@ -1256,9 +1438,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>用于小程序端展示划线价；</t>
         </r>
@@ -1268,9 +1452,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>设置打包费金额，用于外卖、自提等业务收取打包费；</t>
         </r>
@@ -1280,9 +1466,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务指定价格；
 2、未设置时以售价执行</t>
@@ -1293,9 +1481,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">1、自提业务指定价格；
 2、未设置时以售价执行
@@ -1307,9 +1497,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务指定价格；
 2、未设置时以售价执行</t>
@@ -1320,9 +1512,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务的会员价格；
 2、未设置时以会员价执行；
@@ -1334,9 +1528,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、自提业务的会员价格；
 2、未设置时以会员价执行；
@@ -1348,9 +1544,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务的会员价格；
 2、未设置时以会员价执行；
@@ -1362,9 +1560,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商品的堂食会员价；
 2、外卖会员价、自提会员价、商城会员价未设置时以该价格执行；
@@ -1376,9 +1576,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>用于小程序端展示划线价；</t>
         </r>
@@ -1388,9 +1590,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>设置打包费金额，用于外卖、自提等业务收取打包费；</t>
         </r>
@@ -1400,9 +1604,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务指定价格；
 2、未设置时以售价执行</t>
@@ -1413,9 +1619,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">1、自提业务指定价格；
 2、未设置时以售价执行
@@ -1427,9 +1635,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务指定价格；
 2、未设置时以售价执行</t>
@@ -1440,9 +1650,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务的会员价格；
 2、未设置时以会员价执行；
@@ -1454,9 +1666,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、自提业务的会员价格；
 2、未设置时以会员价执行；
@@ -1468,9 +1682,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务的会员价格；
 2、未设置时以会员价执行；
@@ -1482,9 +1698,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商品的堂食会员价；
 2、外卖会员价、自提会员价、商城会员价未设置时以该价格执行；
@@ -1496,9 +1714,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>用于小程序端展示划线价；</t>
         </r>
@@ -1508,9 +1728,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>设置打包费金额，用于外卖、自提等业务收取打包费；</t>
         </r>
@@ -1520,9 +1742,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务指定价格；
 2、未设置时以售价执行</t>
@@ -1533,9 +1757,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">1、自提业务指定价格；
 2、未设置时以售价执行
@@ -1547,9 +1773,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务指定价格；
 2、未设置时以售价执行</t>
@@ -1560,9 +1788,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务的会员价格；
 2、未设置时以会员价执行；
@@ -1574,9 +1804,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、自提业务的会员价格；
 2、未设置时以会员价执行；
@@ -1588,9 +1820,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务的会员价格；
 2、未设置时以会员价执行；
@@ -1602,9 +1836,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商品的堂食会员价；
 2、外卖会员价、自提会员价、商城会员价未设置时以该价格执行；
@@ -1616,9 +1852,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>用于小程序端展示划线价；</t>
         </r>
@@ -1628,9 +1866,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>设置打包费金额，用于外卖、自提等业务收取打包费；</t>
         </r>
@@ -1640,9 +1880,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务指定价格；
 2、未设置时以售价执行</t>
@@ -1653,9 +1895,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">1、自提业务指定价格；
 2、未设置时以售价执行
@@ -1667,9 +1911,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务指定价格；
 2、未设置时以售价执行</t>
@@ -1680,9 +1926,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务的会员价格；
 2、未设置时以会员价执行；
@@ -1694,9 +1942,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、自提业务的会员价格；
 2、未设置时以会员价执行；
@@ -1708,9 +1958,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务的会员价格；
 2、未设置时以会员价执行；
@@ -1722,9 +1974,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商品的堂食会员价；
 2、外卖会员价、自提会员价、商城会员价未设置时以该价格执行；
@@ -1736,9 +1990,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>用于小程序端展示划线价；</t>
         </r>
@@ -1748,9 +2004,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>设置打包费金额，用于外卖、自提等业务收取打包费；</t>
         </r>
@@ -1760,9 +2018,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务指定价格；
 2、未设置时以售价执行</t>
@@ -1773,9 +2033,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">1、自提业务指定价格；
 2、未设置时以售价执行
@@ -1787,9 +2049,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务指定价格；
 2、未设置时以售价执行</t>
@@ -1800,9 +2064,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务的会员价格；
 2、未设置时以会员价执行；
@@ -1814,9 +2080,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、自提业务的会员价格；
 2、未设置时以会员价执行；
@@ -1828,9 +2096,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务的会员价格；
 2、未设置时以会员价执行；
@@ -1842,9 +2112,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商品的堂食会员价；
 2、外卖会员价、自提会员价、商城会员价未设置时以该价格执行；
@@ -1856,9 +2128,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>用于小程序端展示划线价；</t>
         </r>
@@ -1868,9 +2142,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>设置打包费金额，用于外卖、自提等业务收取打包费；</t>
         </r>
@@ -1880,9 +2156,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务指定价格；
 2、未设置时以售价执行</t>
@@ -1893,9 +2171,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">1、自提业务指定价格；
 2、未设置时以售价执行
@@ -1907,9 +2187,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务指定价格；
 2、未设置时以售价执行</t>
@@ -1920,9 +2202,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务的会员价格；
 2、未设置时以会员价执行；
@@ -1934,9 +2218,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、自提业务的会员价格；
 2、未设置时以会员价执行；
@@ -1948,9 +2234,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务的会员价格；
 2、未设置时以会员价执行；
@@ -1962,9 +2250,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商品的堂食会员价；
 2、外卖会员价、自提会员价、商城会员价未设置时以该价格执行；
@@ -1976,9 +2266,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>用于小程序端展示划线价；</t>
         </r>
@@ -1988,9 +2280,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>设置打包费金额，用于外卖、自提等业务收取打包费；</t>
         </r>
@@ -2000,9 +2294,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务指定价格；
 2、未设置时以售价执行</t>
@@ -2013,9 +2309,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">1、自提业务指定价格；
 2、未设置时以售价执行
@@ -2027,9 +2325,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务指定价格；
 2、未设置时以售价执行</t>
@@ -2040,9 +2340,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务的会员价格；
 2、未设置时以会员价执行；
@@ -2054,9 +2356,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、自提业务的会员价格；
 2、未设置时以会员价执行；
@@ -2068,9 +2372,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务的会员价格；
 2、未设置时以会员价执行；
@@ -2082,9 +2388,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商品的堂食会员价；
 2、外卖会员价、自提会员价、商城会员价未设置时以该价格执行；
@@ -2096,9 +2404,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>用于小程序端展示划线价；</t>
         </r>
@@ -2108,9 +2418,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>设置打包费金额，用于外卖、自提等业务收取打包费；</t>
         </r>
@@ -2120,9 +2432,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务指定价格；
 2、未设置时以售价执行</t>
@@ -2133,9 +2447,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">1、自提业务指定价格；
 2、未设置时以售价执行
@@ -2147,9 +2463,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务指定价格；
 2、未设置时以售价执行</t>
@@ -2160,9 +2478,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务的会员价格；
 2、未设置时以会员价执行；
@@ -2174,9 +2494,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、自提业务的会员价格；
 2、未设置时以会员价执行；
@@ -2188,9 +2510,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务的会员价格；
 2、未设置时以会员价执行；
@@ -2202,9 +2526,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商品的堂食会员价；
 2、外卖会员价、自提会员价、商城会员价未设置时以该价格执行；
@@ -2216,9 +2542,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>用于小程序端展示划线价；</t>
         </r>
@@ -2228,9 +2556,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>设置打包费金额，用于外卖、自提等业务收取打包费；</t>
         </r>
@@ -2240,9 +2570,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务指定价格；
 2、未设置时以售价执行</t>
@@ -2253,9 +2585,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">1、自提业务指定价格；
 2、未设置时以售价执行
@@ -2267,9 +2601,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务指定价格；
 2、未设置时以售价执行</t>
@@ -2280,9 +2616,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务的会员价格；
 2、未设置时以会员价执行；
@@ -2294,9 +2632,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、自提业务的会员价格；
 2、未设置时以会员价执行；
@@ -2308,9 +2648,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务的会员价格；
 2、未设置时以会员价执行；
@@ -2322,9 +2664,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商品的堂食会员价；
 2、外卖会员价、自提会员价、商城会员价未设置时以该价格执行；
@@ -2336,9 +2680,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>用于小程序端展示划线价；</t>
         </r>
@@ -2348,9 +2694,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>设置打包费金额，用于外卖、自提等业务收取打包费；</t>
         </r>
@@ -2360,9 +2708,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务指定价格；
 2、未设置时以售价执行</t>
@@ -2373,9 +2723,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">1、自提业务指定价格；
 2、未设置时以售价执行
@@ -2387,9 +2739,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务指定价格；
 2、未设置时以售价执行</t>
@@ -2400,9 +2754,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务的会员价格；
 2、未设置时以会员价执行；
@@ -2414,9 +2770,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、自提业务的会员价格；
 2、未设置时以会员价执行；
@@ -2428,9 +2786,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务的会员价格；
 2、未设置时以会员价执行；
@@ -2452,9 +2812,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商品的堂食会员价；
 2、外卖会员价、自提会员价、商城会员价未设置时以该价格执行；
@@ -2466,9 +2828,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>用于小程序端展示划线价；</t>
         </r>
@@ -2478,9 +2842,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>设置打包费金额，用于外卖、自提等业务收取打包费；</t>
         </r>
@@ -2490,9 +2856,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务指定价格；
 2、未设置时以售价执行</t>
@@ -2503,9 +2871,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">1、自提业务指定价格；
 2、未设置时以售价执行
@@ -2517,9 +2887,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务指定价格；
 2、未设置时以售价执行</t>
@@ -2530,9 +2902,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、外卖业务的会员价格；
 2、未设置时以会员价执行；
@@ -2544,9 +2918,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、自提业务的会员价格；
 2、未设置时以会员价执行；
@@ -2558,9 +2934,11 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>1、商城业务的会员价格；
 2、未设置时以会员价执行；
@@ -2573,40 +2951,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="130">
-  <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>商品导入模板使用说明：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1. 此模板适用于餐品（不包含口味做法、加料信息）、标品、套餐的导入；
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="94">
+  <si>
+    <t>商品导入模板使用说明：
+1. 此模板适用于餐品（不包含口味做法、加料信息）、标品、套餐的导入；
 2. 单次最多支持导入4000个餐品、4000个标品、套餐数据最多4000行；
 3. 请勿更改sheet页名称,请勿更改列名称；
 4 单元格为空代表不设置该商品的属性，系统将按默认值进行导入，具体默认值，请参看商品数据sheet页的字段说明；
 5. 导入会忽略系统中已存在的商品数据；</t>
-    </r>
   </si>
   <si>
     <t>1、商品销售编码：如需要系统自动生成，请保持整列为空；编码规则系统默认为2,2,3；
@@ -2616,51 +2968,12 @@
 5、品牌名称：品牌的档案，必须在系统里存在，商品档案才能导入系统；</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">1、单规格商品，请填写规格1的相应价格；
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2、多规格商品:可填写规格1~3的相应规格及价格，如需更多规格可取消表格隐藏，显示规格4~10；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
+    <t>1、单规格商品，请填写规格1的相应价格；
+2、多规格商品:可填写规格1~3的相应规格及价格，如需更多规格可取消表格隐藏，显示规格4~10；
 3、是否称重售卖：只有称重单位的才能填写“是”，例如斤、公斤、克；
 4、规格编码：不填写，系统将自动生成，规格编码不能重复；
 5、条形码：填写格式为69001,69002,69003；
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>6、价格：最多支持两位小数，售价必填，如需填写“外卖售价、自提售价、商城售价、外卖会员价、自提会员价、商城会员价”，可取消表格隐藏；</t>
-    </r>
+6、价格：最多支持两位小数，售价必填，如需填写“外卖售价、自提售价、商城售价、外卖会员价、自提会员价、商城会员价”，可取消表格隐藏；</t>
   </si>
   <si>
     <t>1、打印设置：请填写打印、不打印、同销售分类设置；不填写，默认“同销售分类设置”；
@@ -2720,101 +3033,19 @@
     <t>商品销售编码</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>商品销售名称</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>品牌名称</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>销售分类</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>线上分类</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单位名称</t>
-    </r>
+    <t>*商品销售名称</t>
+  </si>
+  <si>
+    <t>*品牌名称</t>
+  </si>
+  <si>
+    <t>*销售分类</t>
+  </si>
+  <si>
+    <t>*线上分类</t>
+  </si>
+  <si>
+    <t>*单位名称</t>
   </si>
   <si>
     <t>是否称重售卖</t>
@@ -2826,24 +3057,7 @@
     <t>条形码</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>售价</t>
-    </r>
+    <t>*售价</t>
   </si>
   <si>
     <t>会员价</t>
@@ -2948,52 +3162,25 @@
     <t>查询标签</t>
   </si>
   <si>
-    <t>西红柿炒鸡蛋</t>
-  </si>
-  <si>
-    <t>通用品牌</t>
-  </si>
-  <si>
-    <t>热菜</t>
+    <t>测试可颂</t>
+  </si>
+  <si>
+    <t>可颂 Croissant</t>
+  </si>
+  <si>
+    <t>个</t>
+  </si>
+  <si>
+    <t>堂食+外卖+外带+自提</t>
+  </si>
+  <si>
+    <t>是</t>
+  </si>
+  <si>
+    <t>在售</t>
   </si>
   <si>
     <t>否</t>
-  </si>
-  <si>
-    <t>打印</t>
-  </si>
-  <si>
-    <t>热菜打印档口</t>
-  </si>
-  <si>
-    <t>堂食+外卖+外带+自提</t>
-  </si>
-  <si>
-    <t>是</t>
-  </si>
-  <si>
-    <t>在售</t>
-  </si>
-  <si>
-    <t>热销+特色+招牌</t>
-  </si>
-  <si>
-    <t>不辣</t>
-  </si>
-  <si>
-    <t>辣椒炒肉</t>
-  </si>
-  <si>
-    <t>份</t>
-  </si>
-  <si>
-    <t>不打印</t>
-  </si>
-  <si>
-    <t>停售</t>
-  </si>
-  <si>
-    <t>同销售分类设置</t>
   </si>
   <si>
     <t>1、商品销售编码：如需要系统自动生成，请保持整列为空；编码规则系统默认为2,2,3；
@@ -3003,36 +3190,8 @@
 5、品牌名称：品牌的档案，必须在系统里存在，商品档案才能导入系统；</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">1、单规格商品，请填写规格1的相应价格；
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2、多规格商品:可填写规格1~3的相应规格及价格，如需更多规格可取消表格隐藏，显示规格4~10；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
+    <t>1、单规格商品，请填写规格1的相应价格；
+2、多规格商品:可填写规格1~3的相应规格及价格，如需更多规格可取消表格隐藏，显示规格4~10；
 3、门店是否可销售：以可口可乐为例，有瓶和箱的单位，门店销售瓶的单位，那么将瓶设置为可销售（填写是），箱填写“否”；
 4、是否标准单位：同一个商品存在多单位，以可口可乐为例，有瓶和箱的单位，那么将瓶设置为标准单位（填写是），箱填写“否”；
 5、单位系数：例如可口可乐有瓶、箱、毫升的单位，瓶是标准单位；1箱=24瓶，1瓶=250毫升；(罐填写信息：标准单位系数=1，非标准单位系数=1)；(箱填写信息：标准单位系数=24，非标准单位系数=1)；(毫升填写信息：标准单位系数=1，非标准单位系数=250)；
@@ -3040,27 +3199,9 @@
 7、规格编码：不填写，系统将自动生成，规格编码不能重复；
 8、条形码：填写格式为69001,69002,69003；
 9、价格：最多支持两位小数，是否可销售=是，售价必填；其他的价格字段根据实际情况进行填写；</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>门店是否可销售</t>
-    </r>
+  </si>
+  <si>
+    <t>*门店是否可销售</t>
   </si>
   <si>
     <t>是否标准单位</t>
@@ -3072,53 +3213,13 @@
     <t>非标准单位系数</t>
   </si>
   <si>
-    <t>可口可乐</t>
-  </si>
-  <si>
-    <t>饮品</t>
-  </si>
-  <si>
-    <t>瓶</t>
-  </si>
-  <si>
-    <t>箱</t>
-  </si>
-  <si>
-    <t>毫升</t>
-  </si>
-  <si>
-    <t>酸奶</t>
-  </si>
-  <si>
-    <t>纯奶</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">1、商品销售编码：如需要系统自动生成，请保持整列为空；编码规则系统默认为2,2,3；
+    <t>1、商品销售编码：如需要系统自动生成，请保持整列为空；编码规则系统默认为2,2,3；
 2、商品销售名称：不超过200个字符；
 3、销售分类：如系统中没有分类信息，系统会自动创建；
 4、线上分类：如果商品不在小程序和大屏上架，线上分类可不填写，如果需要在小程序、大屏上架线上分类均需填写，如系统中没有分类信息，系统会自动创建；
 5、品牌名称：品牌的档案，必须在系统里存在，商品档案才能导入系统；
 6、套餐价格分摊方式：只能填写实时售价分摊和明细商品执行单价分摊，如果填写了“明细商品执行单价分摊”，那么“明细商品信息里的套餐执行单价必须填写”；
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>7、套餐的基本信息、单位价格信息、打印设置、其他信息以每个套餐的第一行信息为准；套餐分组信息以每个套餐分组的第一行信息为准；</t>
-    </r>
+7、套餐的基本信息、单位价格信息、打印设置、其他信息以每个套餐的第一行信息为准；套餐分组信息以每个套餐分组的第一行信息为准；</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -3180,74 +3281,14 @@
     <t>套餐执行单价</t>
   </si>
   <si>
-    <t>69元套餐</t>
-  </si>
-  <si>
-    <t>实时售价分摊</t>
-  </si>
-  <si>
-    <t>菜品分组</t>
-  </si>
-  <si>
-    <t>固定搭配</t>
-  </si>
-  <si>
-    <t>凉拌土豆丝</t>
-  </si>
-  <si>
-    <t>主食分组</t>
-  </si>
-  <si>
-    <t>可选搭配</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>白面馒头</t>
-  </si>
-  <si>
-    <t>个</t>
-  </si>
-  <si>
-    <t>米饭</t>
-  </si>
-  <si>
-    <t>碗</t>
-  </si>
-  <si>
-    <t>杂粮馒头</t>
-  </si>
-  <si>
-    <t>饮品任选</t>
-  </si>
-  <si>
-    <t>任选搭配</t>
-  </si>
-  <si>
-    <t>雪碧</t>
-  </si>
-  <si>
-    <t>39元套餐</t>
-  </si>
-  <si>
-    <t>明细商品执行单价分摊</t>
-  </si>
-  <si>
-    <t>凉拌三丝</t>
-  </si>
-  <si>
-    <t>玉米馒头</t>
-  </si>
-  <si>
-    <t>黑米馒头</t>
+    <t>REFEEL·BAKERY</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="18">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3330,39 +3371,17 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Helvetica"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Helvetica"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -3496,7 +3515,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3548,86 +3567,56 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="49" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3826,7 +3815,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="16"/>
       <tableStyleElement type="headerRow" dxfId="15"/>
       <tableStyleElement type="totalRow" dxfId="14"/>
@@ -3835,7 +3824,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="11"/>
       <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="headerRow" dxfId="9"/>
       <tableStyleElement type="totalRow" dxfId="8"/>
       <tableStyleElement type="firstRowStripe" dxfId="7"/>
@@ -4113,23 +4102,23 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15" ht="174" customHeight="1">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4189,384 +4178,385 @@
     <col min="173" max="173" width="16.1640625" style="4" customWidth="1"/>
     <col min="174" max="174" width="21.33203125" style="4" customWidth="1"/>
     <col min="175" max="175" width="15.5" style="4" customWidth="1"/>
-    <col min="176" max="176" width="9.1640625" style="4"/>
+    <col min="176" max="176" width="9.1640625" style="4" customWidth="1"/>
     <col min="177" max="180" width="10.33203125" style="4" customWidth="1"/>
-    <col min="181" max="16384" width="9.1640625" style="4"/>
+    <col min="181" max="181" width="9.1640625" style="4" customWidth="1"/>
+    <col min="182" max="16384" width="9.1640625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:180" ht="132" customHeight="1">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="23" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
-      <c r="R1" s="24"/>
-      <c r="S1" s="24"/>
-      <c r="T1" s="24"/>
-      <c r="U1" s="24"/>
-      <c r="V1" s="24"/>
-      <c r="W1" s="24"/>
-      <c r="X1" s="24"/>
-      <c r="Y1" s="24"/>
-      <c r="Z1" s="24"/>
-      <c r="AA1" s="24"/>
-      <c r="AB1" s="24"/>
-      <c r="AC1" s="24"/>
-      <c r="AD1" s="24"/>
-      <c r="AE1" s="24"/>
-      <c r="AF1" s="24"/>
-      <c r="AG1" s="24"/>
-      <c r="AH1" s="24"/>
-      <c r="AI1" s="24"/>
-      <c r="AJ1" s="24"/>
-      <c r="AK1" s="24"/>
-      <c r="AL1" s="24"/>
-      <c r="AM1" s="24"/>
-      <c r="AN1" s="24"/>
-      <c r="AO1" s="24"/>
-      <c r="AP1" s="24"/>
-      <c r="AQ1" s="24"/>
-      <c r="AR1" s="24"/>
-      <c r="AS1" s="24"/>
-      <c r="AT1" s="24"/>
-      <c r="AU1" s="24"/>
-      <c r="AV1" s="24"/>
-      <c r="AW1" s="24"/>
-      <c r="AX1" s="24"/>
-      <c r="AY1" s="24"/>
-      <c r="AZ1" s="24"/>
-      <c r="BA1" s="24"/>
-      <c r="BB1" s="24"/>
-      <c r="BC1" s="24"/>
-      <c r="BD1" s="24"/>
-      <c r="BE1" s="24"/>
-      <c r="BF1" s="24"/>
-      <c r="BG1" s="24"/>
-      <c r="BH1" s="24"/>
-      <c r="BI1" s="24"/>
-      <c r="BJ1" s="24"/>
-      <c r="BK1" s="24"/>
-      <c r="BL1" s="24"/>
-      <c r="BM1" s="24"/>
-      <c r="BN1" s="24"/>
-      <c r="BO1" s="24"/>
-      <c r="BP1" s="24"/>
-      <c r="BQ1" s="24"/>
-      <c r="BR1" s="24"/>
-      <c r="BS1" s="24"/>
-      <c r="BT1" s="24"/>
-      <c r="BU1" s="24"/>
-      <c r="BV1" s="24"/>
-      <c r="BW1" s="24"/>
-      <c r="BX1" s="24"/>
-      <c r="BY1" s="24"/>
-      <c r="BZ1" s="24"/>
-      <c r="CA1" s="24"/>
-      <c r="CB1" s="24"/>
-      <c r="CC1" s="24"/>
-      <c r="CD1" s="24"/>
-      <c r="CE1" s="24"/>
-      <c r="CF1" s="24"/>
-      <c r="CG1" s="24"/>
-      <c r="CH1" s="24"/>
-      <c r="CI1" s="24"/>
-      <c r="CJ1" s="24"/>
-      <c r="CK1" s="24"/>
-      <c r="CL1" s="24"/>
-      <c r="CM1" s="24"/>
-      <c r="CN1" s="24"/>
-      <c r="CO1" s="24"/>
-      <c r="CP1" s="24"/>
-      <c r="CQ1" s="24"/>
-      <c r="CR1" s="24"/>
-      <c r="CS1" s="24"/>
-      <c r="CT1" s="24"/>
-      <c r="CU1" s="24"/>
-      <c r="CV1" s="24"/>
-      <c r="CW1" s="24"/>
-      <c r="CX1" s="24"/>
-      <c r="CY1" s="24"/>
-      <c r="CZ1" s="24"/>
-      <c r="DA1" s="24"/>
-      <c r="DB1" s="24"/>
-      <c r="DC1" s="24"/>
-      <c r="DD1" s="24"/>
-      <c r="DE1" s="24"/>
-      <c r="DF1" s="24"/>
-      <c r="DG1" s="24"/>
-      <c r="DH1" s="24"/>
-      <c r="DI1" s="24"/>
-      <c r="DJ1" s="24"/>
-      <c r="DK1" s="24"/>
-      <c r="DL1" s="24"/>
-      <c r="DM1" s="24"/>
-      <c r="DN1" s="24"/>
-      <c r="DO1" s="24"/>
-      <c r="DP1" s="24"/>
-      <c r="DQ1" s="24"/>
-      <c r="DR1" s="24"/>
-      <c r="DS1" s="24"/>
-      <c r="DT1" s="24"/>
-      <c r="DU1" s="24"/>
-      <c r="DV1" s="24"/>
-      <c r="DW1" s="24"/>
-      <c r="DX1" s="24"/>
-      <c r="DY1" s="24"/>
-      <c r="DZ1" s="24"/>
-      <c r="EA1" s="24"/>
-      <c r="EB1" s="24"/>
-      <c r="EC1" s="24"/>
-      <c r="ED1" s="24"/>
-      <c r="EE1" s="24"/>
-      <c r="EF1" s="24"/>
-      <c r="EG1" s="24"/>
-      <c r="EH1" s="24"/>
-      <c r="EI1" s="24"/>
-      <c r="EJ1" s="24"/>
-      <c r="EK1" s="24"/>
-      <c r="EL1" s="24"/>
-      <c r="EM1" s="24"/>
-      <c r="EN1" s="24"/>
-      <c r="EO1" s="24"/>
-      <c r="EP1" s="24"/>
-      <c r="EQ1" s="24"/>
-      <c r="ER1" s="24"/>
-      <c r="ES1" s="24"/>
-      <c r="ET1" s="24"/>
-      <c r="EU1" s="24"/>
-      <c r="EV1" s="24"/>
-      <c r="EW1" s="24"/>
-      <c r="EX1" s="24"/>
-      <c r="EY1" s="25"/>
-      <c r="EZ1" s="21" t="s">
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="20"/>
+      <c r="Z1" s="20"/>
+      <c r="AA1" s="20"/>
+      <c r="AB1" s="20"/>
+      <c r="AC1" s="20"/>
+      <c r="AD1" s="20"/>
+      <c r="AE1" s="20"/>
+      <c r="AF1" s="20"/>
+      <c r="AG1" s="20"/>
+      <c r="AH1" s="20"/>
+      <c r="AI1" s="20"/>
+      <c r="AJ1" s="20"/>
+      <c r="AK1" s="20"/>
+      <c r="AL1" s="20"/>
+      <c r="AM1" s="20"/>
+      <c r="AN1" s="20"/>
+      <c r="AO1" s="20"/>
+      <c r="AP1" s="20"/>
+      <c r="AQ1" s="20"/>
+      <c r="AR1" s="20"/>
+      <c r="AS1" s="20"/>
+      <c r="AT1" s="20"/>
+      <c r="AU1" s="20"/>
+      <c r="AV1" s="20"/>
+      <c r="AW1" s="20"/>
+      <c r="AX1" s="20"/>
+      <c r="AY1" s="20"/>
+      <c r="AZ1" s="20"/>
+      <c r="BA1" s="20"/>
+      <c r="BB1" s="20"/>
+      <c r="BC1" s="20"/>
+      <c r="BD1" s="20"/>
+      <c r="BE1" s="20"/>
+      <c r="BF1" s="20"/>
+      <c r="BG1" s="20"/>
+      <c r="BH1" s="20"/>
+      <c r="BI1" s="20"/>
+      <c r="BJ1" s="20"/>
+      <c r="BK1" s="20"/>
+      <c r="BL1" s="20"/>
+      <c r="BM1" s="20"/>
+      <c r="BN1" s="20"/>
+      <c r="BO1" s="20"/>
+      <c r="BP1" s="20"/>
+      <c r="BQ1" s="20"/>
+      <c r="BR1" s="20"/>
+      <c r="BS1" s="20"/>
+      <c r="BT1" s="20"/>
+      <c r="BU1" s="20"/>
+      <c r="BV1" s="20"/>
+      <c r="BW1" s="20"/>
+      <c r="BX1" s="20"/>
+      <c r="BY1" s="20"/>
+      <c r="BZ1" s="20"/>
+      <c r="CA1" s="20"/>
+      <c r="CB1" s="20"/>
+      <c r="CC1" s="20"/>
+      <c r="CD1" s="20"/>
+      <c r="CE1" s="20"/>
+      <c r="CF1" s="20"/>
+      <c r="CG1" s="20"/>
+      <c r="CH1" s="20"/>
+      <c r="CI1" s="20"/>
+      <c r="CJ1" s="20"/>
+      <c r="CK1" s="20"/>
+      <c r="CL1" s="20"/>
+      <c r="CM1" s="20"/>
+      <c r="CN1" s="20"/>
+      <c r="CO1" s="20"/>
+      <c r="CP1" s="20"/>
+      <c r="CQ1" s="20"/>
+      <c r="CR1" s="20"/>
+      <c r="CS1" s="20"/>
+      <c r="CT1" s="20"/>
+      <c r="CU1" s="20"/>
+      <c r="CV1" s="20"/>
+      <c r="CW1" s="20"/>
+      <c r="CX1" s="20"/>
+      <c r="CY1" s="20"/>
+      <c r="CZ1" s="20"/>
+      <c r="DA1" s="20"/>
+      <c r="DB1" s="20"/>
+      <c r="DC1" s="20"/>
+      <c r="DD1" s="20"/>
+      <c r="DE1" s="20"/>
+      <c r="DF1" s="20"/>
+      <c r="DG1" s="20"/>
+      <c r="DH1" s="20"/>
+      <c r="DI1" s="20"/>
+      <c r="DJ1" s="20"/>
+      <c r="DK1" s="20"/>
+      <c r="DL1" s="20"/>
+      <c r="DM1" s="20"/>
+      <c r="DN1" s="20"/>
+      <c r="DO1" s="20"/>
+      <c r="DP1" s="20"/>
+      <c r="DQ1" s="20"/>
+      <c r="DR1" s="20"/>
+      <c r="DS1" s="20"/>
+      <c r="DT1" s="20"/>
+      <c r="DU1" s="20"/>
+      <c r="DV1" s="20"/>
+      <c r="DW1" s="20"/>
+      <c r="DX1" s="20"/>
+      <c r="DY1" s="20"/>
+      <c r="DZ1" s="20"/>
+      <c r="EA1" s="20"/>
+      <c r="EB1" s="20"/>
+      <c r="EC1" s="20"/>
+      <c r="ED1" s="20"/>
+      <c r="EE1" s="20"/>
+      <c r="EF1" s="20"/>
+      <c r="EG1" s="20"/>
+      <c r="EH1" s="20"/>
+      <c r="EI1" s="20"/>
+      <c r="EJ1" s="20"/>
+      <c r="EK1" s="20"/>
+      <c r="EL1" s="20"/>
+      <c r="EM1" s="20"/>
+      <c r="EN1" s="20"/>
+      <c r="EO1" s="20"/>
+      <c r="EP1" s="20"/>
+      <c r="EQ1" s="20"/>
+      <c r="ER1" s="20"/>
+      <c r="ES1" s="20"/>
+      <c r="ET1" s="20"/>
+      <c r="EU1" s="20"/>
+      <c r="EV1" s="20"/>
+      <c r="EW1" s="20"/>
+      <c r="EX1" s="20"/>
+      <c r="EY1" s="21"/>
+      <c r="EZ1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="FA1" s="22"/>
-      <c r="FB1" s="26" t="s">
+      <c r="FA1" s="21"/>
+      <c r="FB1" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="FC1" s="26"/>
-      <c r="FD1" s="26"/>
-      <c r="FE1" s="26"/>
-      <c r="FF1" s="26"/>
-      <c r="FG1" s="26"/>
-      <c r="FH1" s="26"/>
-      <c r="FI1" s="26"/>
-      <c r="FJ1" s="26"/>
-      <c r="FK1" s="27"/>
-      <c r="FL1" s="27"/>
-      <c r="FM1" s="27"/>
-      <c r="FN1" s="27"/>
-      <c r="FO1" s="27"/>
-      <c r="FP1" s="27"/>
-      <c r="FQ1" s="27"/>
-      <c r="FR1" s="27"/>
-      <c r="FS1" s="27"/>
-      <c r="FT1" s="27"/>
-      <c r="FU1" s="27"/>
-      <c r="FV1" s="27"/>
-      <c r="FW1" s="27"/>
-      <c r="FX1" s="27"/>
+      <c r="FC1" s="20"/>
+      <c r="FD1" s="20"/>
+      <c r="FE1" s="20"/>
+      <c r="FF1" s="20"/>
+      <c r="FG1" s="20"/>
+      <c r="FH1" s="20"/>
+      <c r="FI1" s="20"/>
+      <c r="FJ1" s="20"/>
+      <c r="FK1" s="20"/>
+      <c r="FL1" s="20"/>
+      <c r="FM1" s="20"/>
+      <c r="FN1" s="20"/>
+      <c r="FO1" s="20"/>
+      <c r="FP1" s="20"/>
+      <c r="FQ1" s="20"/>
+      <c r="FR1" s="20"/>
+      <c r="FS1" s="20"/>
+      <c r="FT1" s="20"/>
+      <c r="FU1" s="20"/>
+      <c r="FV1" s="20"/>
+      <c r="FW1" s="20"/>
+      <c r="FX1" s="21"/>
     </row>
     <row r="2" spans="1:180" ht="18.25" customHeight="1">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="30" t="s">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
-      <c r="M2" s="31"/>
-      <c r="N2" s="31"/>
-      <c r="O2" s="31"/>
-      <c r="P2" s="31"/>
-      <c r="Q2" s="31"/>
-      <c r="R2" s="31"/>
-      <c r="S2" s="31"/>
-      <c r="T2" s="31"/>
-      <c r="U2" s="30" t="s">
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="V2" s="31"/>
-      <c r="W2" s="31"/>
-      <c r="X2" s="31"/>
-      <c r="Y2" s="31"/>
-      <c r="Z2" s="31"/>
-      <c r="AA2" s="31"/>
-      <c r="AB2" s="31"/>
-      <c r="AC2" s="31"/>
-      <c r="AD2" s="31"/>
-      <c r="AE2" s="31"/>
-      <c r="AF2" s="31"/>
-      <c r="AG2" s="31"/>
-      <c r="AH2" s="31"/>
-      <c r="AI2" s="32"/>
-      <c r="AJ2" s="30" t="s">
+      <c r="V2" s="20"/>
+      <c r="W2" s="20"/>
+      <c r="X2" s="20"/>
+      <c r="Y2" s="20"/>
+      <c r="Z2" s="20"/>
+      <c r="AA2" s="20"/>
+      <c r="AB2" s="20"/>
+      <c r="AC2" s="20"/>
+      <c r="AD2" s="20"/>
+      <c r="AE2" s="20"/>
+      <c r="AF2" s="20"/>
+      <c r="AG2" s="20"/>
+      <c r="AH2" s="20"/>
+      <c r="AI2" s="21"/>
+      <c r="AJ2" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="AK2" s="31"/>
-      <c r="AL2" s="31"/>
-      <c r="AM2" s="31"/>
-      <c r="AN2" s="31"/>
-      <c r="AO2" s="31"/>
-      <c r="AP2" s="31"/>
-      <c r="AQ2" s="31"/>
-      <c r="AR2" s="31"/>
-      <c r="AS2" s="31"/>
-      <c r="AT2" s="31"/>
-      <c r="AU2" s="31"/>
-      <c r="AV2" s="31"/>
-      <c r="AW2" s="31"/>
-      <c r="AX2" s="32"/>
-      <c r="AY2" s="30" t="s">
+      <c r="AK2" s="20"/>
+      <c r="AL2" s="20"/>
+      <c r="AM2" s="20"/>
+      <c r="AN2" s="20"/>
+      <c r="AO2" s="20"/>
+      <c r="AP2" s="20"/>
+      <c r="AQ2" s="20"/>
+      <c r="AR2" s="20"/>
+      <c r="AS2" s="20"/>
+      <c r="AT2" s="20"/>
+      <c r="AU2" s="20"/>
+      <c r="AV2" s="20"/>
+      <c r="AW2" s="20"/>
+      <c r="AX2" s="21"/>
+      <c r="AY2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="AZ2" s="31"/>
-      <c r="BA2" s="31"/>
-      <c r="BB2" s="31"/>
-      <c r="BC2" s="31"/>
-      <c r="BD2" s="31"/>
-      <c r="BE2" s="31"/>
-      <c r="BF2" s="31"/>
-      <c r="BG2" s="31"/>
-      <c r="BH2" s="31"/>
-      <c r="BI2" s="31"/>
-      <c r="BJ2" s="31"/>
-      <c r="BK2" s="31"/>
-      <c r="BL2" s="31"/>
-      <c r="BM2" s="32"/>
-      <c r="BN2" s="30" t="s">
+      <c r="AZ2" s="20"/>
+      <c r="BA2" s="20"/>
+      <c r="BB2" s="20"/>
+      <c r="BC2" s="20"/>
+      <c r="BD2" s="20"/>
+      <c r="BE2" s="20"/>
+      <c r="BF2" s="20"/>
+      <c r="BG2" s="20"/>
+      <c r="BH2" s="20"/>
+      <c r="BI2" s="20"/>
+      <c r="BJ2" s="20"/>
+      <c r="BK2" s="20"/>
+      <c r="BL2" s="20"/>
+      <c r="BM2" s="21"/>
+      <c r="BN2" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="BO2" s="31"/>
-      <c r="BP2" s="31"/>
-      <c r="BQ2" s="31"/>
-      <c r="BR2" s="31"/>
-      <c r="BS2" s="31"/>
-      <c r="BT2" s="31"/>
-      <c r="BU2" s="31"/>
-      <c r="BV2" s="31"/>
-      <c r="BW2" s="31"/>
-      <c r="BX2" s="31"/>
-      <c r="BY2" s="31"/>
-      <c r="BZ2" s="31"/>
-      <c r="CA2" s="31"/>
-      <c r="CB2" s="32"/>
-      <c r="CC2" s="30" t="s">
+      <c r="BO2" s="20"/>
+      <c r="BP2" s="20"/>
+      <c r="BQ2" s="20"/>
+      <c r="BR2" s="20"/>
+      <c r="BS2" s="20"/>
+      <c r="BT2" s="20"/>
+      <c r="BU2" s="20"/>
+      <c r="BV2" s="20"/>
+      <c r="BW2" s="20"/>
+      <c r="BX2" s="20"/>
+      <c r="BY2" s="20"/>
+      <c r="BZ2" s="20"/>
+      <c r="CA2" s="20"/>
+      <c r="CB2" s="21"/>
+      <c r="CC2" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="CD2" s="31"/>
-      <c r="CE2" s="31"/>
-      <c r="CF2" s="31"/>
-      <c r="CG2" s="31"/>
-      <c r="CH2" s="31"/>
-      <c r="CI2" s="31"/>
-      <c r="CJ2" s="31"/>
-      <c r="CK2" s="31"/>
-      <c r="CL2" s="31"/>
-      <c r="CM2" s="31"/>
-      <c r="CN2" s="31"/>
-      <c r="CO2" s="31"/>
-      <c r="CP2" s="31"/>
-      <c r="CQ2" s="32"/>
-      <c r="CR2" s="30" t="s">
+      <c r="CD2" s="20"/>
+      <c r="CE2" s="20"/>
+      <c r="CF2" s="20"/>
+      <c r="CG2" s="20"/>
+      <c r="CH2" s="20"/>
+      <c r="CI2" s="20"/>
+      <c r="CJ2" s="20"/>
+      <c r="CK2" s="20"/>
+      <c r="CL2" s="20"/>
+      <c r="CM2" s="20"/>
+      <c r="CN2" s="20"/>
+      <c r="CO2" s="20"/>
+      <c r="CP2" s="20"/>
+      <c r="CQ2" s="21"/>
+      <c r="CR2" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="CS2" s="31"/>
-      <c r="CT2" s="31"/>
-      <c r="CU2" s="31"/>
-      <c r="CV2" s="31"/>
-      <c r="CW2" s="31"/>
-      <c r="CX2" s="31"/>
-      <c r="CY2" s="31"/>
-      <c r="CZ2" s="31"/>
-      <c r="DA2" s="31"/>
-      <c r="DB2" s="31"/>
-      <c r="DC2" s="31"/>
-      <c r="DD2" s="31"/>
-      <c r="DE2" s="31"/>
-      <c r="DF2" s="32"/>
-      <c r="DG2" s="30" t="s">
+      <c r="CS2" s="20"/>
+      <c r="CT2" s="20"/>
+      <c r="CU2" s="20"/>
+      <c r="CV2" s="20"/>
+      <c r="CW2" s="20"/>
+      <c r="CX2" s="20"/>
+      <c r="CY2" s="20"/>
+      <c r="CZ2" s="20"/>
+      <c r="DA2" s="20"/>
+      <c r="DB2" s="20"/>
+      <c r="DC2" s="20"/>
+      <c r="DD2" s="20"/>
+      <c r="DE2" s="20"/>
+      <c r="DF2" s="21"/>
+      <c r="DG2" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="DH2" s="31"/>
-      <c r="DI2" s="31"/>
-      <c r="DJ2" s="31"/>
-      <c r="DK2" s="31"/>
-      <c r="DL2" s="31"/>
-      <c r="DM2" s="31"/>
-      <c r="DN2" s="31"/>
-      <c r="DO2" s="31"/>
-      <c r="DP2" s="31"/>
-      <c r="DQ2" s="31"/>
-      <c r="DR2" s="31"/>
-      <c r="DS2" s="31"/>
-      <c r="DT2" s="31"/>
-      <c r="DU2" s="32"/>
-      <c r="DV2" s="30" t="s">
+      <c r="DH2" s="20"/>
+      <c r="DI2" s="20"/>
+      <c r="DJ2" s="20"/>
+      <c r="DK2" s="20"/>
+      <c r="DL2" s="20"/>
+      <c r="DM2" s="20"/>
+      <c r="DN2" s="20"/>
+      <c r="DO2" s="20"/>
+      <c r="DP2" s="20"/>
+      <c r="DQ2" s="20"/>
+      <c r="DR2" s="20"/>
+      <c r="DS2" s="20"/>
+      <c r="DT2" s="20"/>
+      <c r="DU2" s="21"/>
+      <c r="DV2" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="DW2" s="31"/>
-      <c r="DX2" s="31"/>
-      <c r="DY2" s="31"/>
-      <c r="DZ2" s="31"/>
-      <c r="EA2" s="31"/>
-      <c r="EB2" s="31"/>
-      <c r="EC2" s="31"/>
-      <c r="ED2" s="31"/>
-      <c r="EE2" s="31"/>
-      <c r="EF2" s="31"/>
-      <c r="EG2" s="31"/>
-      <c r="EH2" s="31"/>
-      <c r="EI2" s="31"/>
-      <c r="EJ2" s="32"/>
-      <c r="EK2" s="30" t="s">
+      <c r="DW2" s="20"/>
+      <c r="DX2" s="20"/>
+      <c r="DY2" s="20"/>
+      <c r="DZ2" s="20"/>
+      <c r="EA2" s="20"/>
+      <c r="EB2" s="20"/>
+      <c r="EC2" s="20"/>
+      <c r="ED2" s="20"/>
+      <c r="EE2" s="20"/>
+      <c r="EF2" s="20"/>
+      <c r="EG2" s="20"/>
+      <c r="EH2" s="20"/>
+      <c r="EI2" s="20"/>
+      <c r="EJ2" s="21"/>
+      <c r="EK2" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="EL2" s="31"/>
-      <c r="EM2" s="31"/>
-      <c r="EN2" s="31"/>
-      <c r="EO2" s="31"/>
-      <c r="EP2" s="31"/>
-      <c r="EQ2" s="31"/>
-      <c r="ER2" s="31"/>
-      <c r="ES2" s="31"/>
-      <c r="ET2" s="31"/>
-      <c r="EU2" s="31"/>
-      <c r="EV2" s="31"/>
-      <c r="EW2" s="31"/>
-      <c r="EX2" s="31"/>
-      <c r="EY2" s="31"/>
+      <c r="EL2" s="20"/>
+      <c r="EM2" s="20"/>
+      <c r="EN2" s="20"/>
+      <c r="EO2" s="20"/>
+      <c r="EP2" s="20"/>
+      <c r="EQ2" s="20"/>
+      <c r="ER2" s="20"/>
+      <c r="ES2" s="20"/>
+      <c r="ET2" s="20"/>
+      <c r="EU2" s="20"/>
+      <c r="EV2" s="20"/>
+      <c r="EW2" s="20"/>
+      <c r="EX2" s="20"/>
+      <c r="EY2" s="20"/>
       <c r="EZ2" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="FA2" s="29"/>
-      <c r="FB2" s="20" t="s">
+      <c r="FA2" s="20"/>
+      <c r="FB2" s="27" t="s">
         <v>17</v>
       </c>
       <c r="FC2" s="20"/>
@@ -4590,9 +4580,9 @@
       <c r="FU2" s="20"/>
       <c r="FV2" s="20"/>
       <c r="FW2" s="20"/>
-      <c r="FX2" s="20"/>
+      <c r="FX2" s="21"/>
     </row>
-    <row r="3" spans="1:180" ht="16">
+    <row r="3" spans="1:180" ht="16" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>18</v>
       </c>
@@ -5134,17 +5124,29 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:180" ht="16">
+    <row r="4" spans="1:180" ht="16" customHeight="1">
       <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+      <c r="B4" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
+      <c r="J4" s="3">
+        <v>1000</v>
+      </c>
       <c r="K4" s="12"/>
       <c r="L4" s="12"/>
       <c r="M4" s="12"/>
@@ -5290,61 +5292,61 @@
       <c r="EW4" s="12"/>
       <c r="EX4" s="12"/>
       <c r="EY4" s="12"/>
-      <c r="EZ4" s="43"/>
+      <c r="EZ4" s="17"/>
       <c r="FA4" s="12"/>
       <c r="FB4" s="12"/>
       <c r="FC4" s="12"/>
       <c r="FD4" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="FE4" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="FF4" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="FG4" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="FH4" s="3"/>
       <c r="FI4" s="3"/>
       <c r="FJ4" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="FK4" s="12"/>
       <c r="FL4" s="12"/>
       <c r="FM4" s="12"/>
       <c r="FN4" s="12" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="FO4" s="12" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="FP4" s="12" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="FQ4" s="12"/>
       <c r="FR4" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="FB1:FX1"/>
+    <mergeCell ref="CC2:CQ2"/>
+    <mergeCell ref="F1:EY1"/>
+    <mergeCell ref="BN2:CB2"/>
+    <mergeCell ref="FB2:FX2"/>
+    <mergeCell ref="CR2:DF2"/>
+    <mergeCell ref="DG2:DU2"/>
+    <mergeCell ref="DV2:EJ2"/>
+    <mergeCell ref="F2:T2"/>
+    <mergeCell ref="EK2:EY2"/>
+    <mergeCell ref="EZ1:FA1"/>
     <mergeCell ref="EZ2:FA2"/>
-    <mergeCell ref="FB2:FX2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="F1:EY1"/>
-    <mergeCell ref="EZ1:FA1"/>
-    <mergeCell ref="FB1:FX1"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="F2:T2"/>
     <mergeCell ref="U2:AI2"/>
     <mergeCell ref="AJ2:AX2"/>
     <mergeCell ref="AY2:BM2"/>
-    <mergeCell ref="BN2:CB2"/>
-    <mergeCell ref="CC2:CQ2"/>
-    <mergeCell ref="CR2:DF2"/>
-    <mergeCell ref="DG2:DU2"/>
-    <mergeCell ref="DV2:EJ2"/>
-    <mergeCell ref="EK2:EY2"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing r:id="rId1"/>
@@ -5353,7 +5355,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:HB6"/>
+  <dimension ref="A1:HB3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.1640625" style="4" customWidth="1"/>
@@ -5425,7 +5427,7 @@
     <col min="175" max="185" width="13.6640625" style="4" hidden="1" customWidth="1"/>
     <col min="186" max="186" width="18.83203125" style="4" customWidth="1"/>
     <col min="187" max="187" width="21.33203125" style="4" customWidth="1"/>
-    <col min="188" max="188" width="9.1640625" style="4"/>
+    <col min="188" max="188" width="9.1640625" style="4" customWidth="1"/>
     <col min="189" max="189" width="11" style="4" customWidth="1"/>
     <col min="190" max="190" width="26.6640625" style="4" customWidth="1"/>
     <col min="191" max="191" width="10.5" style="4" customWidth="1"/>
@@ -5437,442 +5439,443 @@
     <col min="202" max="202" width="24" style="4" customWidth="1"/>
     <col min="203" max="203" width="11" style="4" customWidth="1"/>
     <col min="204" max="204" width="19.6640625" style="4" customWidth="1"/>
-    <col min="205" max="16384" width="9.1640625" style="4"/>
+    <col min="205" max="205" width="9.1640625" style="4" customWidth="1"/>
+    <col min="206" max="16384" width="9.1640625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:210" ht="137" customHeight="1">
-      <c r="A1" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
-      <c r="R1" s="24"/>
-      <c r="S1" s="24"/>
-      <c r="T1" s="24"/>
-      <c r="U1" s="24"/>
-      <c r="V1" s="24"/>
-      <c r="W1" s="24"/>
-      <c r="X1" s="24"/>
-      <c r="Y1" s="24"/>
-      <c r="Z1" s="24"/>
-      <c r="AA1" s="24"/>
-      <c r="AB1" s="24"/>
-      <c r="AC1" s="24"/>
-      <c r="AD1" s="24"/>
-      <c r="AE1" s="24"/>
-      <c r="AF1" s="24"/>
-      <c r="AG1" s="24"/>
-      <c r="AH1" s="24"/>
-      <c r="AI1" s="24"/>
-      <c r="AJ1" s="24"/>
-      <c r="AK1" s="24"/>
-      <c r="AL1" s="24"/>
-      <c r="AM1" s="24"/>
-      <c r="AN1" s="24"/>
-      <c r="AO1" s="24"/>
-      <c r="AP1" s="24"/>
-      <c r="AQ1" s="24"/>
-      <c r="AR1" s="24"/>
-      <c r="AS1" s="24"/>
-      <c r="AT1" s="24"/>
-      <c r="AU1" s="24"/>
-      <c r="AV1" s="24"/>
-      <c r="AW1" s="24"/>
-      <c r="AX1" s="24"/>
-      <c r="AY1" s="24"/>
-      <c r="AZ1" s="24"/>
-      <c r="BA1" s="24"/>
-      <c r="BB1" s="24"/>
-      <c r="BC1" s="24"/>
-      <c r="BD1" s="24"/>
-      <c r="BE1" s="24"/>
-      <c r="BF1" s="24"/>
-      <c r="BG1" s="24"/>
-      <c r="BH1" s="24"/>
-      <c r="BI1" s="24"/>
-      <c r="BJ1" s="24"/>
-      <c r="BK1" s="24"/>
-      <c r="BL1" s="24"/>
-      <c r="BM1" s="24"/>
-      <c r="BN1" s="24"/>
-      <c r="BO1" s="24"/>
-      <c r="BP1" s="24"/>
-      <c r="BQ1" s="24"/>
-      <c r="BR1" s="24"/>
-      <c r="BS1" s="24"/>
-      <c r="BT1" s="24"/>
-      <c r="BU1" s="24"/>
-      <c r="BV1" s="24"/>
-      <c r="BW1" s="24"/>
-      <c r="BX1" s="24"/>
-      <c r="BY1" s="24"/>
-      <c r="BZ1" s="24"/>
-      <c r="CA1" s="24"/>
-      <c r="CB1" s="24"/>
-      <c r="CC1" s="24"/>
-      <c r="CD1" s="24"/>
-      <c r="CE1" s="24"/>
-      <c r="CF1" s="24"/>
-      <c r="CG1" s="24"/>
-      <c r="CH1" s="24"/>
-      <c r="CI1" s="24"/>
-      <c r="CJ1" s="24"/>
-      <c r="CK1" s="24"/>
-      <c r="CL1" s="24"/>
-      <c r="CM1" s="24"/>
-      <c r="CN1" s="24"/>
-      <c r="CO1" s="24"/>
-      <c r="CP1" s="24"/>
-      <c r="CQ1" s="24"/>
-      <c r="CR1" s="24"/>
-      <c r="CS1" s="24"/>
-      <c r="CT1" s="24"/>
-      <c r="CU1" s="24"/>
-      <c r="CV1" s="24"/>
-      <c r="CW1" s="24"/>
-      <c r="CX1" s="24"/>
-      <c r="CY1" s="24"/>
-      <c r="CZ1" s="24"/>
-      <c r="DA1" s="24"/>
-      <c r="DB1" s="24"/>
-      <c r="DC1" s="24"/>
-      <c r="DD1" s="24"/>
-      <c r="DE1" s="24"/>
-      <c r="DF1" s="24"/>
-      <c r="DG1" s="24"/>
-      <c r="DH1" s="24"/>
-      <c r="DI1" s="24"/>
-      <c r="DJ1" s="24"/>
-      <c r="DK1" s="24"/>
-      <c r="DL1" s="24"/>
-      <c r="DM1" s="24"/>
-      <c r="DN1" s="24"/>
-      <c r="DO1" s="24"/>
-      <c r="DP1" s="24"/>
-      <c r="DQ1" s="24"/>
-      <c r="DR1" s="24"/>
-      <c r="DS1" s="24"/>
-      <c r="DT1" s="24"/>
-      <c r="DU1" s="24"/>
-      <c r="DV1" s="24"/>
-      <c r="DW1" s="24"/>
-      <c r="DX1" s="24"/>
-      <c r="DY1" s="24"/>
-      <c r="DZ1" s="24"/>
-      <c r="EA1" s="24"/>
-      <c r="EB1" s="24"/>
-      <c r="EC1" s="24"/>
-      <c r="ED1" s="24"/>
-      <c r="EE1" s="24"/>
-      <c r="EF1" s="24"/>
-      <c r="EG1" s="24"/>
-      <c r="EH1" s="24"/>
-      <c r="EI1" s="24"/>
-      <c r="EJ1" s="24"/>
-      <c r="EK1" s="24"/>
-      <c r="EL1" s="24"/>
-      <c r="EM1" s="24"/>
-      <c r="EN1" s="24"/>
-      <c r="EO1" s="24"/>
-      <c r="EP1" s="24"/>
-      <c r="EQ1" s="24"/>
-      <c r="ER1" s="24"/>
-      <c r="ES1" s="24"/>
-      <c r="ET1" s="24"/>
-      <c r="EU1" s="24"/>
-      <c r="EV1" s="24"/>
-      <c r="EW1" s="24"/>
-      <c r="EX1" s="24"/>
-      <c r="EY1" s="24"/>
-      <c r="EZ1" s="24"/>
-      <c r="FA1" s="24"/>
-      <c r="FB1" s="24"/>
-      <c r="FC1" s="24"/>
-      <c r="FD1" s="24"/>
-      <c r="FE1" s="24"/>
-      <c r="FF1" s="24"/>
-      <c r="FG1" s="24"/>
-      <c r="FH1" s="24"/>
-      <c r="FI1" s="24"/>
-      <c r="FJ1" s="24"/>
-      <c r="FK1" s="24"/>
-      <c r="FL1" s="24"/>
-      <c r="FM1" s="24"/>
-      <c r="FN1" s="24"/>
-      <c r="FO1" s="24"/>
-      <c r="FP1" s="24"/>
-      <c r="FQ1" s="24"/>
-      <c r="FR1" s="24"/>
-      <c r="FS1" s="24"/>
-      <c r="FT1" s="24"/>
-      <c r="FU1" s="24"/>
-      <c r="FV1" s="24"/>
-      <c r="FW1" s="24"/>
-      <c r="FX1" s="24"/>
-      <c r="FY1" s="24"/>
-      <c r="FZ1" s="24"/>
-      <c r="GA1" s="24"/>
-      <c r="GB1" s="24"/>
-      <c r="GC1" s="24"/>
-      <c r="GD1" s="21" t="s">
+      <c r="A1" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="20"/>
+      <c r="Z1" s="20"/>
+      <c r="AA1" s="20"/>
+      <c r="AB1" s="20"/>
+      <c r="AC1" s="20"/>
+      <c r="AD1" s="20"/>
+      <c r="AE1" s="20"/>
+      <c r="AF1" s="20"/>
+      <c r="AG1" s="20"/>
+      <c r="AH1" s="20"/>
+      <c r="AI1" s="20"/>
+      <c r="AJ1" s="20"/>
+      <c r="AK1" s="20"/>
+      <c r="AL1" s="20"/>
+      <c r="AM1" s="20"/>
+      <c r="AN1" s="20"/>
+      <c r="AO1" s="20"/>
+      <c r="AP1" s="20"/>
+      <c r="AQ1" s="20"/>
+      <c r="AR1" s="20"/>
+      <c r="AS1" s="20"/>
+      <c r="AT1" s="20"/>
+      <c r="AU1" s="20"/>
+      <c r="AV1" s="20"/>
+      <c r="AW1" s="20"/>
+      <c r="AX1" s="20"/>
+      <c r="AY1" s="20"/>
+      <c r="AZ1" s="20"/>
+      <c r="BA1" s="20"/>
+      <c r="BB1" s="20"/>
+      <c r="BC1" s="20"/>
+      <c r="BD1" s="20"/>
+      <c r="BE1" s="20"/>
+      <c r="BF1" s="20"/>
+      <c r="BG1" s="20"/>
+      <c r="BH1" s="20"/>
+      <c r="BI1" s="20"/>
+      <c r="BJ1" s="20"/>
+      <c r="BK1" s="20"/>
+      <c r="BL1" s="20"/>
+      <c r="BM1" s="20"/>
+      <c r="BN1" s="20"/>
+      <c r="BO1" s="20"/>
+      <c r="BP1" s="20"/>
+      <c r="BQ1" s="20"/>
+      <c r="BR1" s="20"/>
+      <c r="BS1" s="20"/>
+      <c r="BT1" s="20"/>
+      <c r="BU1" s="20"/>
+      <c r="BV1" s="20"/>
+      <c r="BW1" s="20"/>
+      <c r="BX1" s="20"/>
+      <c r="BY1" s="20"/>
+      <c r="BZ1" s="20"/>
+      <c r="CA1" s="20"/>
+      <c r="CB1" s="20"/>
+      <c r="CC1" s="20"/>
+      <c r="CD1" s="20"/>
+      <c r="CE1" s="20"/>
+      <c r="CF1" s="20"/>
+      <c r="CG1" s="20"/>
+      <c r="CH1" s="20"/>
+      <c r="CI1" s="20"/>
+      <c r="CJ1" s="20"/>
+      <c r="CK1" s="20"/>
+      <c r="CL1" s="20"/>
+      <c r="CM1" s="20"/>
+      <c r="CN1" s="20"/>
+      <c r="CO1" s="20"/>
+      <c r="CP1" s="20"/>
+      <c r="CQ1" s="20"/>
+      <c r="CR1" s="20"/>
+      <c r="CS1" s="20"/>
+      <c r="CT1" s="20"/>
+      <c r="CU1" s="20"/>
+      <c r="CV1" s="20"/>
+      <c r="CW1" s="20"/>
+      <c r="CX1" s="20"/>
+      <c r="CY1" s="20"/>
+      <c r="CZ1" s="20"/>
+      <c r="DA1" s="20"/>
+      <c r="DB1" s="20"/>
+      <c r="DC1" s="20"/>
+      <c r="DD1" s="20"/>
+      <c r="DE1" s="20"/>
+      <c r="DF1" s="20"/>
+      <c r="DG1" s="20"/>
+      <c r="DH1" s="20"/>
+      <c r="DI1" s="20"/>
+      <c r="DJ1" s="20"/>
+      <c r="DK1" s="20"/>
+      <c r="DL1" s="20"/>
+      <c r="DM1" s="20"/>
+      <c r="DN1" s="20"/>
+      <c r="DO1" s="20"/>
+      <c r="DP1" s="20"/>
+      <c r="DQ1" s="20"/>
+      <c r="DR1" s="20"/>
+      <c r="DS1" s="20"/>
+      <c r="DT1" s="20"/>
+      <c r="DU1" s="20"/>
+      <c r="DV1" s="20"/>
+      <c r="DW1" s="20"/>
+      <c r="DX1" s="20"/>
+      <c r="DY1" s="20"/>
+      <c r="DZ1" s="20"/>
+      <c r="EA1" s="20"/>
+      <c r="EB1" s="20"/>
+      <c r="EC1" s="20"/>
+      <c r="ED1" s="20"/>
+      <c r="EE1" s="20"/>
+      <c r="EF1" s="20"/>
+      <c r="EG1" s="20"/>
+      <c r="EH1" s="20"/>
+      <c r="EI1" s="20"/>
+      <c r="EJ1" s="20"/>
+      <c r="EK1" s="20"/>
+      <c r="EL1" s="20"/>
+      <c r="EM1" s="20"/>
+      <c r="EN1" s="20"/>
+      <c r="EO1" s="20"/>
+      <c r="EP1" s="20"/>
+      <c r="EQ1" s="20"/>
+      <c r="ER1" s="20"/>
+      <c r="ES1" s="20"/>
+      <c r="ET1" s="20"/>
+      <c r="EU1" s="20"/>
+      <c r="EV1" s="20"/>
+      <c r="EW1" s="20"/>
+      <c r="EX1" s="20"/>
+      <c r="EY1" s="20"/>
+      <c r="EZ1" s="20"/>
+      <c r="FA1" s="20"/>
+      <c r="FB1" s="20"/>
+      <c r="FC1" s="20"/>
+      <c r="FD1" s="20"/>
+      <c r="FE1" s="20"/>
+      <c r="FF1" s="20"/>
+      <c r="FG1" s="20"/>
+      <c r="FH1" s="20"/>
+      <c r="FI1" s="20"/>
+      <c r="FJ1" s="20"/>
+      <c r="FK1" s="20"/>
+      <c r="FL1" s="20"/>
+      <c r="FM1" s="20"/>
+      <c r="FN1" s="20"/>
+      <c r="FO1" s="20"/>
+      <c r="FP1" s="20"/>
+      <c r="FQ1" s="20"/>
+      <c r="FR1" s="20"/>
+      <c r="FS1" s="20"/>
+      <c r="FT1" s="20"/>
+      <c r="FU1" s="20"/>
+      <c r="FV1" s="20"/>
+      <c r="FW1" s="20"/>
+      <c r="FX1" s="20"/>
+      <c r="FY1" s="20"/>
+      <c r="FZ1" s="20"/>
+      <c r="GA1" s="20"/>
+      <c r="GB1" s="20"/>
+      <c r="GC1" s="20"/>
+      <c r="GD1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="GE1" s="22"/>
-      <c r="GF1" s="33" t="s">
+      <c r="GE1" s="21"/>
+      <c r="GF1" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="GG1" s="34"/>
-      <c r="GH1" s="34"/>
-      <c r="GI1" s="34"/>
-      <c r="GJ1" s="34"/>
-      <c r="GK1" s="34"/>
-      <c r="GL1" s="34"/>
-      <c r="GM1" s="34"/>
-      <c r="GN1" s="34"/>
-      <c r="GO1" s="34"/>
-      <c r="GP1" s="34"/>
-      <c r="GQ1" s="34"/>
-      <c r="GR1" s="34"/>
-      <c r="GS1" s="34"/>
-      <c r="GT1" s="34"/>
-      <c r="GU1" s="34"/>
-      <c r="GV1" s="34"/>
-      <c r="GW1" s="34"/>
-      <c r="GX1" s="34"/>
-      <c r="GY1" s="34"/>
-      <c r="GZ1" s="34"/>
-      <c r="HA1" s="34"/>
-      <c r="HB1" s="34"/>
+      <c r="GG1" s="31"/>
+      <c r="GH1" s="31"/>
+      <c r="GI1" s="31"/>
+      <c r="GJ1" s="31"/>
+      <c r="GK1" s="31"/>
+      <c r="GL1" s="31"/>
+      <c r="GM1" s="31"/>
+      <c r="GN1" s="31"/>
+      <c r="GO1" s="31"/>
+      <c r="GP1" s="31"/>
+      <c r="GQ1" s="31"/>
+      <c r="GR1" s="31"/>
+      <c r="GS1" s="31"/>
+      <c r="GT1" s="31"/>
+      <c r="GU1" s="31"/>
+      <c r="GV1" s="31"/>
+      <c r="GW1" s="31"/>
+      <c r="GX1" s="31"/>
+      <c r="GY1" s="31"/>
+      <c r="GZ1" s="31"/>
+      <c r="HA1" s="31"/>
+      <c r="HB1" s="31"/>
     </row>
-    <row r="2" spans="1:210" ht="16">
-      <c r="A2" s="30" t="s">
+    <row r="2" spans="1:210" ht="16" customHeight="1">
+      <c r="A2" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="35" t="s">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
-      <c r="T2" s="35"/>
-      <c r="U2" s="35"/>
-      <c r="V2" s="35"/>
-      <c r="W2" s="35"/>
-      <c r="X2" s="35" t="s">
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
+      <c r="V2" s="20"/>
+      <c r="W2" s="21"/>
+      <c r="X2" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="Y2" s="35"/>
-      <c r="Z2" s="35"/>
-      <c r="AA2" s="35"/>
-      <c r="AB2" s="35"/>
-      <c r="AC2" s="35"/>
-      <c r="AD2" s="35"/>
-      <c r="AE2" s="35"/>
-      <c r="AF2" s="35"/>
-      <c r="AG2" s="35"/>
-      <c r="AH2" s="35"/>
-      <c r="AI2" s="35"/>
-      <c r="AJ2" s="35"/>
-      <c r="AK2" s="35"/>
-      <c r="AL2" s="35"/>
-      <c r="AM2" s="35"/>
-      <c r="AN2" s="35"/>
-      <c r="AO2" s="35"/>
-      <c r="AP2" s="35" t="s">
+      <c r="Y2" s="20"/>
+      <c r="Z2" s="20"/>
+      <c r="AA2" s="20"/>
+      <c r="AB2" s="20"/>
+      <c r="AC2" s="20"/>
+      <c r="AD2" s="20"/>
+      <c r="AE2" s="20"/>
+      <c r="AF2" s="20"/>
+      <c r="AG2" s="20"/>
+      <c r="AH2" s="20"/>
+      <c r="AI2" s="20"/>
+      <c r="AJ2" s="20"/>
+      <c r="AK2" s="20"/>
+      <c r="AL2" s="20"/>
+      <c r="AM2" s="20"/>
+      <c r="AN2" s="20"/>
+      <c r="AO2" s="21"/>
+      <c r="AP2" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="AQ2" s="35"/>
-      <c r="AR2" s="35"/>
-      <c r="AS2" s="35"/>
-      <c r="AT2" s="35"/>
-      <c r="AU2" s="35"/>
-      <c r="AV2" s="35"/>
-      <c r="AW2" s="35"/>
-      <c r="AX2" s="35"/>
-      <c r="AY2" s="35"/>
-      <c r="AZ2" s="35"/>
-      <c r="BA2" s="35"/>
-      <c r="BB2" s="35"/>
-      <c r="BC2" s="35"/>
-      <c r="BD2" s="35"/>
-      <c r="BE2" s="35"/>
-      <c r="BF2" s="35"/>
-      <c r="BG2" s="35"/>
-      <c r="BH2" s="35" t="s">
+      <c r="AQ2" s="20"/>
+      <c r="AR2" s="20"/>
+      <c r="AS2" s="20"/>
+      <c r="AT2" s="20"/>
+      <c r="AU2" s="20"/>
+      <c r="AV2" s="20"/>
+      <c r="AW2" s="20"/>
+      <c r="AX2" s="20"/>
+      <c r="AY2" s="20"/>
+      <c r="AZ2" s="20"/>
+      <c r="BA2" s="20"/>
+      <c r="BB2" s="20"/>
+      <c r="BC2" s="20"/>
+      <c r="BD2" s="20"/>
+      <c r="BE2" s="20"/>
+      <c r="BF2" s="20"/>
+      <c r="BG2" s="21"/>
+      <c r="BH2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="BI2" s="35"/>
-      <c r="BJ2" s="35"/>
-      <c r="BK2" s="35"/>
-      <c r="BL2" s="35"/>
-      <c r="BM2" s="35"/>
-      <c r="BN2" s="35"/>
-      <c r="BO2" s="35"/>
-      <c r="BP2" s="35"/>
-      <c r="BQ2" s="35"/>
-      <c r="BR2" s="35"/>
-      <c r="BS2" s="35"/>
-      <c r="BT2" s="35"/>
-      <c r="BU2" s="35"/>
-      <c r="BV2" s="35"/>
-      <c r="BW2" s="35"/>
-      <c r="BX2" s="35"/>
-      <c r="BY2" s="35"/>
-      <c r="BZ2" s="35" t="s">
+      <c r="BI2" s="20"/>
+      <c r="BJ2" s="20"/>
+      <c r="BK2" s="20"/>
+      <c r="BL2" s="20"/>
+      <c r="BM2" s="20"/>
+      <c r="BN2" s="20"/>
+      <c r="BO2" s="20"/>
+      <c r="BP2" s="20"/>
+      <c r="BQ2" s="20"/>
+      <c r="BR2" s="20"/>
+      <c r="BS2" s="20"/>
+      <c r="BT2" s="20"/>
+      <c r="BU2" s="20"/>
+      <c r="BV2" s="20"/>
+      <c r="BW2" s="20"/>
+      <c r="BX2" s="20"/>
+      <c r="BY2" s="21"/>
+      <c r="BZ2" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="CA2" s="35"/>
-      <c r="CB2" s="35"/>
-      <c r="CC2" s="35"/>
-      <c r="CD2" s="35"/>
-      <c r="CE2" s="35"/>
-      <c r="CF2" s="35"/>
-      <c r="CG2" s="35"/>
-      <c r="CH2" s="35"/>
-      <c r="CI2" s="35"/>
-      <c r="CJ2" s="35"/>
-      <c r="CK2" s="35"/>
-      <c r="CL2" s="35"/>
-      <c r="CM2" s="35"/>
-      <c r="CN2" s="35"/>
-      <c r="CO2" s="35"/>
-      <c r="CP2" s="35"/>
-      <c r="CQ2" s="35"/>
-      <c r="CR2" s="35" t="s">
+      <c r="CA2" s="20"/>
+      <c r="CB2" s="20"/>
+      <c r="CC2" s="20"/>
+      <c r="CD2" s="20"/>
+      <c r="CE2" s="20"/>
+      <c r="CF2" s="20"/>
+      <c r="CG2" s="20"/>
+      <c r="CH2" s="20"/>
+      <c r="CI2" s="20"/>
+      <c r="CJ2" s="20"/>
+      <c r="CK2" s="20"/>
+      <c r="CL2" s="20"/>
+      <c r="CM2" s="20"/>
+      <c r="CN2" s="20"/>
+      <c r="CO2" s="20"/>
+      <c r="CP2" s="20"/>
+      <c r="CQ2" s="21"/>
+      <c r="CR2" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="CS2" s="35"/>
-      <c r="CT2" s="35"/>
-      <c r="CU2" s="35"/>
-      <c r="CV2" s="35"/>
-      <c r="CW2" s="35"/>
-      <c r="CX2" s="35"/>
-      <c r="CY2" s="35"/>
-      <c r="CZ2" s="35"/>
-      <c r="DA2" s="35"/>
-      <c r="DB2" s="35"/>
-      <c r="DC2" s="35"/>
-      <c r="DD2" s="35"/>
-      <c r="DE2" s="35"/>
-      <c r="DF2" s="35"/>
-      <c r="DG2" s="35"/>
-      <c r="DH2" s="35"/>
-      <c r="DI2" s="35"/>
-      <c r="DJ2" s="35" t="s">
+      <c r="CS2" s="20"/>
+      <c r="CT2" s="20"/>
+      <c r="CU2" s="20"/>
+      <c r="CV2" s="20"/>
+      <c r="CW2" s="20"/>
+      <c r="CX2" s="20"/>
+      <c r="CY2" s="20"/>
+      <c r="CZ2" s="20"/>
+      <c r="DA2" s="20"/>
+      <c r="DB2" s="20"/>
+      <c r="DC2" s="20"/>
+      <c r="DD2" s="20"/>
+      <c r="DE2" s="20"/>
+      <c r="DF2" s="20"/>
+      <c r="DG2" s="20"/>
+      <c r="DH2" s="20"/>
+      <c r="DI2" s="21"/>
+      <c r="DJ2" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="DK2" s="35"/>
-      <c r="DL2" s="35"/>
-      <c r="DM2" s="35"/>
-      <c r="DN2" s="35"/>
-      <c r="DO2" s="35"/>
-      <c r="DP2" s="35"/>
-      <c r="DQ2" s="35"/>
-      <c r="DR2" s="35"/>
-      <c r="DS2" s="35"/>
-      <c r="DT2" s="35"/>
-      <c r="DU2" s="35"/>
-      <c r="DV2" s="35"/>
-      <c r="DW2" s="35"/>
-      <c r="DX2" s="35"/>
-      <c r="DY2" s="35"/>
-      <c r="DZ2" s="35"/>
-      <c r="EA2" s="35"/>
-      <c r="EB2" s="35" t="s">
+      <c r="DK2" s="20"/>
+      <c r="DL2" s="20"/>
+      <c r="DM2" s="20"/>
+      <c r="DN2" s="20"/>
+      <c r="DO2" s="20"/>
+      <c r="DP2" s="20"/>
+      <c r="DQ2" s="20"/>
+      <c r="DR2" s="20"/>
+      <c r="DS2" s="20"/>
+      <c r="DT2" s="20"/>
+      <c r="DU2" s="20"/>
+      <c r="DV2" s="20"/>
+      <c r="DW2" s="20"/>
+      <c r="DX2" s="20"/>
+      <c r="DY2" s="20"/>
+      <c r="DZ2" s="20"/>
+      <c r="EA2" s="21"/>
+      <c r="EB2" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="EC2" s="35"/>
-      <c r="ED2" s="35"/>
-      <c r="EE2" s="35"/>
-      <c r="EF2" s="35"/>
-      <c r="EG2" s="35"/>
-      <c r="EH2" s="35"/>
-      <c r="EI2" s="35"/>
-      <c r="EJ2" s="35"/>
-      <c r="EK2" s="35"/>
-      <c r="EL2" s="35"/>
-      <c r="EM2" s="35"/>
-      <c r="EN2" s="35"/>
-      <c r="EO2" s="35"/>
-      <c r="EP2" s="35"/>
-      <c r="EQ2" s="35"/>
-      <c r="ER2" s="35"/>
-      <c r="ES2" s="35"/>
-      <c r="ET2" s="35" t="s">
+      <c r="EC2" s="20"/>
+      <c r="ED2" s="20"/>
+      <c r="EE2" s="20"/>
+      <c r="EF2" s="20"/>
+      <c r="EG2" s="20"/>
+      <c r="EH2" s="20"/>
+      <c r="EI2" s="20"/>
+      <c r="EJ2" s="20"/>
+      <c r="EK2" s="20"/>
+      <c r="EL2" s="20"/>
+      <c r="EM2" s="20"/>
+      <c r="EN2" s="20"/>
+      <c r="EO2" s="20"/>
+      <c r="EP2" s="20"/>
+      <c r="EQ2" s="20"/>
+      <c r="ER2" s="20"/>
+      <c r="ES2" s="21"/>
+      <c r="ET2" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="EU2" s="35"/>
-      <c r="EV2" s="35"/>
-      <c r="EW2" s="35"/>
-      <c r="EX2" s="35"/>
-      <c r="EY2" s="35"/>
-      <c r="EZ2" s="35"/>
-      <c r="FA2" s="35"/>
-      <c r="FB2" s="35"/>
-      <c r="FC2" s="35"/>
-      <c r="FD2" s="35"/>
-      <c r="FE2" s="35"/>
-      <c r="FF2" s="35"/>
-      <c r="FG2" s="35"/>
-      <c r="FH2" s="35"/>
-      <c r="FI2" s="35"/>
-      <c r="FJ2" s="35"/>
-      <c r="FK2" s="35"/>
-      <c r="FL2" s="35" t="s">
+      <c r="EU2" s="20"/>
+      <c r="EV2" s="20"/>
+      <c r="EW2" s="20"/>
+      <c r="EX2" s="20"/>
+      <c r="EY2" s="20"/>
+      <c r="EZ2" s="20"/>
+      <c r="FA2" s="20"/>
+      <c r="FB2" s="20"/>
+      <c r="FC2" s="20"/>
+      <c r="FD2" s="20"/>
+      <c r="FE2" s="20"/>
+      <c r="FF2" s="20"/>
+      <c r="FG2" s="20"/>
+      <c r="FH2" s="20"/>
+      <c r="FI2" s="20"/>
+      <c r="FJ2" s="20"/>
+      <c r="FK2" s="21"/>
+      <c r="FL2" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="FM2" s="35"/>
-      <c r="FN2" s="35"/>
-      <c r="FO2" s="35"/>
-      <c r="FP2" s="35"/>
-      <c r="FQ2" s="35"/>
-      <c r="FR2" s="35"/>
-      <c r="FS2" s="35"/>
-      <c r="FT2" s="35"/>
-      <c r="FU2" s="35"/>
-      <c r="FV2" s="35"/>
-      <c r="FW2" s="35"/>
-      <c r="FX2" s="35"/>
-      <c r="FY2" s="35"/>
-      <c r="FZ2" s="35"/>
-      <c r="GA2" s="35"/>
-      <c r="GB2" s="35"/>
-      <c r="GC2" s="35"/>
+      <c r="FM2" s="20"/>
+      <c r="FN2" s="20"/>
+      <c r="FO2" s="20"/>
+      <c r="FP2" s="20"/>
+      <c r="FQ2" s="20"/>
+      <c r="FR2" s="20"/>
+      <c r="FS2" s="20"/>
+      <c r="FT2" s="20"/>
+      <c r="FU2" s="20"/>
+      <c r="FV2" s="20"/>
+      <c r="FW2" s="20"/>
+      <c r="FX2" s="20"/>
+      <c r="FY2" s="20"/>
+      <c r="FZ2" s="20"/>
+      <c r="GA2" s="20"/>
+      <c r="GB2" s="20"/>
+      <c r="GC2" s="21"/>
       <c r="GD2" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="GE2" s="29"/>
-      <c r="GF2" s="20" t="s">
+      <c r="GE2" s="20"/>
+      <c r="GF2" s="27" t="s">
         <v>17</v>
       </c>
       <c r="GG2" s="20"/>
@@ -5896,9 +5899,9 @@
       <c r="GY2" s="20"/>
       <c r="GZ2" s="20"/>
       <c r="HA2" s="20"/>
-      <c r="HB2" s="20"/>
+      <c r="HB2" s="21"/>
     </row>
-    <row r="3" spans="1:210" ht="16">
+    <row r="3" spans="1:210" ht="16" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>18</v>
       </c>
@@ -5918,16 +5921,16 @@
         <v>23</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="K3" s="15" t="s">
         <v>24</v>
@@ -5972,16 +5975,16 @@
         <v>23</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="Z3" s="9" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="AA3" s="9" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="AB3" s="7" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AC3" s="15" t="s">
         <v>24</v>
@@ -6026,16 +6029,16 @@
         <v>23</v>
       </c>
       <c r="AQ3" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="AR3" s="9" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="AS3" s="9" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="AT3" s="7" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AU3" s="15" t="s">
         <v>24</v>
@@ -6080,16 +6083,16 @@
         <v>23</v>
       </c>
       <c r="BI3" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="BJ3" s="9" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="BK3" s="9" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="BL3" s="7" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="BM3" s="15" t="s">
         <v>24</v>
@@ -6134,16 +6137,16 @@
         <v>23</v>
       </c>
       <c r="CA3" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="CB3" s="9" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="CC3" s="9" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="CD3" s="7" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="CE3" s="15" t="s">
         <v>24</v>
@@ -6188,16 +6191,16 @@
         <v>23</v>
       </c>
       <c r="CS3" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="CT3" s="9" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="CU3" s="9" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="CV3" s="7" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="CW3" s="15" t="s">
         <v>24</v>
@@ -6242,16 +6245,16 @@
         <v>23</v>
       </c>
       <c r="DK3" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="DL3" s="9" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="DM3" s="9" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="DN3" s="7" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="DO3" s="15" t="s">
         <v>24</v>
@@ -6296,16 +6299,16 @@
         <v>23</v>
       </c>
       <c r="EC3" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="ED3" s="9" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="EE3" s="9" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="EF3" s="7" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="EG3" s="15" t="s">
         <v>24</v>
@@ -6350,16 +6353,16 @@
         <v>23</v>
       </c>
       <c r="EU3" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="EV3" s="9" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="EW3" s="9" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="EX3" s="7" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="EY3" s="15" t="s">
         <v>24</v>
@@ -6404,16 +6407,16 @@
         <v>23</v>
       </c>
       <c r="FM3" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="FN3" s="9" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="FO3" s="9" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="FP3" s="7" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="FQ3" s="15" t="s">
         <v>24</v>
@@ -6529,779 +6532,26 @@
       <c r="HB3" s="14" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="4" spans="1:210" ht="16">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="I4" s="3">
-        <v>1</v>
-      </c>
-      <c r="J4" s="12">
-        <v>1</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="3">
-        <v>3</v>
-      </c>
-      <c r="O4" s="12"/>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12"/>
-      <c r="S4" s="12"/>
-      <c r="T4" s="12"/>
-      <c r="U4" s="12"/>
-      <c r="V4" s="12"/>
-      <c r="W4" s="12"/>
-      <c r="X4" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="Z4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="AA4" s="3">
-        <v>24</v>
-      </c>
-      <c r="AB4" s="12">
-        <v>1</v>
-      </c>
-      <c r="AC4" s="12"/>
-      <c r="AD4" s="12"/>
-      <c r="AE4" s="12"/>
-      <c r="AF4" s="12"/>
-      <c r="AG4" s="12"/>
-      <c r="AH4" s="12"/>
-      <c r="AI4" s="12"/>
-      <c r="AJ4" s="12"/>
-      <c r="AK4" s="12"/>
-      <c r="AL4" s="12"/>
-      <c r="AM4" s="12"/>
-      <c r="AN4" s="12"/>
-      <c r="AO4" s="12"/>
-      <c r="AP4" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="AQ4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="AR4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="AS4" s="3">
-        <v>1</v>
-      </c>
-      <c r="AT4" s="12">
-        <v>250</v>
-      </c>
-      <c r="AU4" s="12"/>
-      <c r="AV4" s="12"/>
-      <c r="AW4" s="12"/>
-      <c r="AX4" s="12"/>
-      <c r="AY4" s="12"/>
-      <c r="AZ4" s="12"/>
-      <c r="BA4" s="12"/>
-      <c r="BB4" s="12"/>
-      <c r="BC4" s="12"/>
-      <c r="BD4" s="12"/>
-      <c r="BE4" s="12"/>
-      <c r="BF4" s="12"/>
-      <c r="BG4" s="12"/>
-      <c r="BH4" s="12"/>
-      <c r="BI4" s="12"/>
-      <c r="BJ4" s="12"/>
-      <c r="BK4" s="12"/>
-      <c r="BL4" s="12"/>
-      <c r="BM4" s="12"/>
-      <c r="BN4" s="12"/>
-      <c r="BO4" s="12"/>
-      <c r="BP4" s="12"/>
-      <c r="BQ4" s="12"/>
-      <c r="BR4" s="12"/>
-      <c r="BS4" s="12"/>
-      <c r="BT4" s="12"/>
-      <c r="BU4" s="12"/>
-      <c r="BV4" s="12"/>
-      <c r="BW4" s="12"/>
-      <c r="BX4" s="12"/>
-      <c r="BY4" s="12"/>
-      <c r="BZ4" s="12"/>
-      <c r="CA4" s="12"/>
-      <c r="CB4" s="12"/>
-      <c r="CC4" s="12"/>
-      <c r="CD4" s="12"/>
-      <c r="CE4" s="12"/>
-      <c r="CF4" s="12"/>
-      <c r="CG4" s="12"/>
-      <c r="CH4" s="12"/>
-      <c r="CI4" s="12"/>
-      <c r="CJ4" s="12"/>
-      <c r="CK4" s="12"/>
-      <c r="CL4" s="12"/>
-      <c r="CM4" s="12"/>
-      <c r="CN4" s="12"/>
-      <c r="CO4" s="12"/>
-      <c r="CP4" s="12"/>
-      <c r="CQ4" s="12"/>
-      <c r="CR4" s="12"/>
-      <c r="CS4" s="12"/>
-      <c r="CT4" s="12"/>
-      <c r="CU4" s="12"/>
-      <c r="CV4" s="12"/>
-      <c r="CW4" s="12"/>
-      <c r="CX4" s="12"/>
-      <c r="CY4" s="12"/>
-      <c r="CZ4" s="12"/>
-      <c r="DA4" s="12"/>
-      <c r="DB4" s="12"/>
-      <c r="DC4" s="12"/>
-      <c r="DD4" s="12"/>
-      <c r="DE4" s="12"/>
-      <c r="DF4" s="12"/>
-      <c r="DG4" s="12"/>
-      <c r="DH4" s="12"/>
-      <c r="DI4" s="12"/>
-      <c r="DJ4" s="12"/>
-      <c r="DK4" s="12"/>
-      <c r="DL4" s="12"/>
-      <c r="DM4" s="12"/>
-      <c r="DN4" s="12"/>
-      <c r="DO4" s="12"/>
-      <c r="DP4" s="12"/>
-      <c r="DQ4" s="12"/>
-      <c r="DR4" s="12"/>
-      <c r="DS4" s="12"/>
-      <c r="DT4" s="12"/>
-      <c r="DU4" s="12"/>
-      <c r="DV4" s="12"/>
-      <c r="DW4" s="12"/>
-      <c r="DX4" s="12"/>
-      <c r="DY4" s="12"/>
-      <c r="DZ4" s="12"/>
-      <c r="EA4" s="12"/>
-      <c r="EB4" s="12"/>
-      <c r="EC4" s="12"/>
-      <c r="ED4" s="12"/>
-      <c r="EE4" s="12"/>
-      <c r="EF4" s="12"/>
-      <c r="EG4" s="12"/>
-      <c r="EH4" s="12"/>
-      <c r="EI4" s="12"/>
-      <c r="EJ4" s="12"/>
-      <c r="EK4" s="12"/>
-      <c r="EL4" s="12"/>
-      <c r="EM4" s="12"/>
-      <c r="EN4" s="12"/>
-      <c r="EO4" s="12"/>
-      <c r="EP4" s="12"/>
-      <c r="EQ4" s="12"/>
-      <c r="ER4" s="12"/>
-      <c r="ES4" s="12"/>
-      <c r="ET4" s="12"/>
-      <c r="EU4" s="12"/>
-      <c r="EV4" s="12"/>
-      <c r="EW4" s="12"/>
-      <c r="EX4" s="12"/>
-      <c r="EY4" s="12"/>
-      <c r="EZ4" s="12"/>
-      <c r="FA4" s="12"/>
-      <c r="FB4" s="12"/>
-      <c r="FC4" s="12"/>
-      <c r="FD4" s="12"/>
-      <c r="FE4" s="12"/>
-      <c r="FF4" s="12"/>
-      <c r="FG4" s="12"/>
-      <c r="FH4" s="12"/>
-      <c r="FI4" s="12"/>
-      <c r="FJ4" s="12"/>
-      <c r="FK4" s="12"/>
-      <c r="FL4" s="12"/>
-      <c r="FM4" s="12"/>
-      <c r="FN4" s="12"/>
-      <c r="FO4" s="12"/>
-      <c r="FP4" s="12"/>
-      <c r="FQ4" s="12"/>
-      <c r="FR4" s="12"/>
-      <c r="FS4" s="12"/>
-      <c r="FT4" s="12"/>
-      <c r="FU4" s="12"/>
-      <c r="FV4" s="12"/>
-      <c r="FW4" s="12"/>
-      <c r="FX4" s="12"/>
-      <c r="FY4" s="12"/>
-      <c r="FZ4" s="12"/>
-      <c r="GA4" s="12"/>
-      <c r="GB4" s="12"/>
-      <c r="GC4" s="12"/>
-      <c r="GD4" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="GE4" s="12"/>
-      <c r="GF4" s="12"/>
-      <c r="GG4" s="12"/>
-      <c r="GH4" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="GI4" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="GJ4" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="GK4" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="GL4" s="3"/>
-      <c r="GM4" s="3"/>
-      <c r="GN4" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="GO4" s="12"/>
-      <c r="GP4" s="12"/>
-      <c r="GQ4" s="12"/>
-      <c r="GR4" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="GS4" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="GT4" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="GU4" s="12"/>
-      <c r="GV4" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="GX4" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:210" ht="16">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="I5" s="3">
-        <v>1</v>
-      </c>
-      <c r="J5" s="12">
-        <v>1</v>
-      </c>
-      <c r="K5" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3">
-        <v>3</v>
-      </c>
-      <c r="O5" s="12"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="12"/>
-      <c r="T5" s="12"/>
-      <c r="U5" s="12"/>
-      <c r="V5" s="12"/>
-      <c r="W5" s="12"/>
-      <c r="X5" s="12"/>
-      <c r="Y5" s="12"/>
-      <c r="Z5" s="12"/>
-      <c r="AA5" s="12"/>
-      <c r="AB5" s="12"/>
-      <c r="AC5" s="12"/>
-      <c r="AD5" s="12"/>
-      <c r="AE5" s="12"/>
-      <c r="AF5" s="12"/>
-      <c r="AG5" s="12"/>
-      <c r="AH5" s="12"/>
-      <c r="AI5" s="12"/>
-      <c r="AJ5" s="12"/>
-      <c r="AK5" s="12"/>
-      <c r="AL5" s="12"/>
-      <c r="AM5" s="12"/>
-      <c r="AN5" s="12"/>
-      <c r="AO5" s="12"/>
-      <c r="AP5" s="12"/>
-      <c r="AQ5" s="12"/>
-      <c r="AR5" s="12"/>
-      <c r="AS5" s="12"/>
-      <c r="AT5" s="12"/>
-      <c r="AU5" s="12"/>
-      <c r="AV5" s="12"/>
-      <c r="AW5" s="12"/>
-      <c r="AX5" s="12"/>
-      <c r="AY5" s="12"/>
-      <c r="AZ5" s="12"/>
-      <c r="BA5" s="12"/>
-      <c r="BB5" s="12"/>
-      <c r="BC5" s="12"/>
-      <c r="BD5" s="12"/>
-      <c r="BE5" s="12"/>
-      <c r="BF5" s="12"/>
-      <c r="BG5" s="12"/>
-      <c r="BH5" s="12"/>
-      <c r="BI5" s="12"/>
-      <c r="BJ5" s="12"/>
-      <c r="BK5" s="12"/>
-      <c r="BL5" s="12"/>
-      <c r="BM5" s="12"/>
-      <c r="BN5" s="12"/>
-      <c r="BO5" s="12"/>
-      <c r="BP5" s="12"/>
-      <c r="BQ5" s="12"/>
-      <c r="BR5" s="12"/>
-      <c r="BS5" s="12"/>
-      <c r="BT5" s="12"/>
-      <c r="BU5" s="12"/>
-      <c r="BV5" s="12"/>
-      <c r="BW5" s="12"/>
-      <c r="BX5" s="12"/>
-      <c r="BY5" s="12"/>
-      <c r="BZ5" s="12"/>
-      <c r="CA5" s="12"/>
-      <c r="CB5" s="12"/>
-      <c r="CC5" s="12"/>
-      <c r="CD5" s="12"/>
-      <c r="CE5" s="12"/>
-      <c r="CF5" s="12"/>
-      <c r="CG5" s="12"/>
-      <c r="CH5" s="12"/>
-      <c r="CI5" s="12"/>
-      <c r="CJ5" s="12"/>
-      <c r="CK5" s="12"/>
-      <c r="CL5" s="12"/>
-      <c r="CM5" s="12"/>
-      <c r="CN5" s="12"/>
-      <c r="CO5" s="12"/>
-      <c r="CP5" s="12"/>
-      <c r="CQ5" s="12"/>
-      <c r="CR5" s="12"/>
-      <c r="CS5" s="12"/>
-      <c r="CT5" s="12"/>
-      <c r="CU5" s="12"/>
-      <c r="CV5" s="12"/>
-      <c r="CW5" s="12"/>
-      <c r="CX5" s="12"/>
-      <c r="CY5" s="12"/>
-      <c r="CZ5" s="12"/>
-      <c r="DA5" s="12"/>
-      <c r="DB5" s="12"/>
-      <c r="DC5" s="12"/>
-      <c r="DD5" s="12"/>
-      <c r="DE5" s="12"/>
-      <c r="DF5" s="12"/>
-      <c r="DG5" s="12"/>
-      <c r="DH5" s="12"/>
-      <c r="DI5" s="12"/>
-      <c r="DJ5" s="12"/>
-      <c r="DK5" s="12"/>
-      <c r="DL5" s="12"/>
-      <c r="DM5" s="12"/>
-      <c r="DN5" s="12"/>
-      <c r="DO5" s="12"/>
-      <c r="DP5" s="12"/>
-      <c r="DQ5" s="12"/>
-      <c r="DR5" s="12"/>
-      <c r="DS5" s="12"/>
-      <c r="DT5" s="12"/>
-      <c r="DU5" s="12"/>
-      <c r="DV5" s="12"/>
-      <c r="DW5" s="12"/>
-      <c r="DX5" s="12"/>
-      <c r="DY5" s="12"/>
-      <c r="DZ5" s="12"/>
-      <c r="EA5" s="12"/>
-      <c r="EB5" s="12"/>
-      <c r="EC5" s="12"/>
-      <c r="ED5" s="12"/>
-      <c r="EE5" s="12"/>
-      <c r="EF5" s="12"/>
-      <c r="EG5" s="12"/>
-      <c r="EH5" s="12"/>
-      <c r="EI5" s="12"/>
-      <c r="EJ5" s="12"/>
-      <c r="EK5" s="12"/>
-      <c r="EL5" s="12"/>
-      <c r="EM5" s="12"/>
-      <c r="EN5" s="12"/>
-      <c r="EO5" s="12"/>
-      <c r="EP5" s="12"/>
-      <c r="EQ5" s="12"/>
-      <c r="ER5" s="12"/>
-      <c r="ES5" s="12"/>
-      <c r="ET5" s="12"/>
-      <c r="EU5" s="12"/>
-      <c r="EV5" s="12"/>
-      <c r="EW5" s="12"/>
-      <c r="EX5" s="12"/>
-      <c r="EY5" s="12"/>
-      <c r="EZ5" s="12"/>
-      <c r="FA5" s="12"/>
-      <c r="FB5" s="12"/>
-      <c r="FC5" s="12"/>
-      <c r="FD5" s="12"/>
-      <c r="FE5" s="12"/>
-      <c r="FF5" s="12"/>
-      <c r="FG5" s="12"/>
-      <c r="FH5" s="12"/>
-      <c r="FI5" s="12"/>
-      <c r="FJ5" s="12"/>
-      <c r="FK5" s="12"/>
-      <c r="FL5" s="12"/>
-      <c r="FM5" s="12"/>
-      <c r="FN5" s="12"/>
-      <c r="FO5" s="12"/>
-      <c r="FP5" s="12"/>
-      <c r="FQ5" s="12"/>
-      <c r="FR5" s="12"/>
-      <c r="FS5" s="12"/>
-      <c r="FT5" s="12"/>
-      <c r="FU5" s="12"/>
-      <c r="FV5" s="12"/>
-      <c r="FW5" s="12"/>
-      <c r="FX5" s="12"/>
-      <c r="FY5" s="12"/>
-      <c r="FZ5" s="12"/>
-      <c r="GA5" s="12"/>
-      <c r="GB5" s="12"/>
-      <c r="GC5" s="12"/>
-      <c r="GD5" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="GE5" s="3"/>
-      <c r="GF5" s="12"/>
-      <c r="GG5" s="12"/>
-      <c r="GH5" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="GI5" s="3"/>
-      <c r="GJ5" s="3"/>
-      <c r="GK5" s="3"/>
-      <c r="GL5" s="3"/>
-      <c r="GM5" s="3"/>
-      <c r="GN5" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="GO5" s="12"/>
-      <c r="GP5" s="12"/>
-      <c r="GQ5" s="12"/>
-      <c r="GR5" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="GS5" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="GT5" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="GU5" s="12"/>
-      <c r="GV5" s="12"/>
-    </row>
-    <row r="6" spans="1:210" ht="16">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="I6" s="3">
-        <v>1</v>
-      </c>
-      <c r="J6" s="12">
-        <v>1</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3">
-        <v>3</v>
-      </c>
-      <c r="O6" s="12"/>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="12"/>
-      <c r="S6" s="12"/>
-      <c r="T6" s="12"/>
-      <c r="U6" s="12"/>
-      <c r="V6" s="12"/>
-      <c r="W6" s="12"/>
-      <c r="X6" s="12"/>
-      <c r="Y6" s="12"/>
-      <c r="Z6" s="12"/>
-      <c r="AA6" s="12"/>
-      <c r="AB6" s="12"/>
-      <c r="AC6" s="12"/>
-      <c r="AD6" s="12"/>
-      <c r="AE6" s="12"/>
-      <c r="AF6" s="12"/>
-      <c r="AG6" s="12"/>
-      <c r="AH6" s="12"/>
-      <c r="AI6" s="12"/>
-      <c r="AJ6" s="12"/>
-      <c r="AK6" s="12"/>
-      <c r="AL6" s="12"/>
-      <c r="AM6" s="12"/>
-      <c r="AN6" s="12"/>
-      <c r="AO6" s="12"/>
-      <c r="AP6" s="12"/>
-      <c r="AQ6" s="12"/>
-      <c r="AR6" s="12"/>
-      <c r="AS6" s="12"/>
-      <c r="AT6" s="12"/>
-      <c r="AU6" s="12"/>
-      <c r="AV6" s="12"/>
-      <c r="AW6" s="12"/>
-      <c r="AX6" s="12"/>
-      <c r="AY6" s="12"/>
-      <c r="AZ6" s="12"/>
-      <c r="BA6" s="12"/>
-      <c r="BB6" s="12"/>
-      <c r="BC6" s="12"/>
-      <c r="BD6" s="12"/>
-      <c r="BE6" s="12"/>
-      <c r="BF6" s="12"/>
-      <c r="BG6" s="12"/>
-      <c r="BH6" s="12"/>
-      <c r="BI6" s="12"/>
-      <c r="BJ6" s="12"/>
-      <c r="BK6" s="12"/>
-      <c r="BL6" s="12"/>
-      <c r="BM6" s="12"/>
-      <c r="BN6" s="12"/>
-      <c r="BO6" s="12"/>
-      <c r="BP6" s="12"/>
-      <c r="BQ6" s="12"/>
-      <c r="BR6" s="12"/>
-      <c r="BS6" s="12"/>
-      <c r="BT6" s="12"/>
-      <c r="BU6" s="12"/>
-      <c r="BV6" s="12"/>
-      <c r="BW6" s="12"/>
-      <c r="BX6" s="12"/>
-      <c r="BY6" s="12"/>
-      <c r="BZ6" s="12"/>
-      <c r="CA6" s="12"/>
-      <c r="CB6" s="12"/>
-      <c r="CC6" s="12"/>
-      <c r="CD6" s="12"/>
-      <c r="CE6" s="12"/>
-      <c r="CF6" s="12"/>
-      <c r="CG6" s="12"/>
-      <c r="CH6" s="12"/>
-      <c r="CI6" s="12"/>
-      <c r="CJ6" s="12"/>
-      <c r="CK6" s="12"/>
-      <c r="CL6" s="12"/>
-      <c r="CM6" s="12"/>
-      <c r="CN6" s="12"/>
-      <c r="CO6" s="12"/>
-      <c r="CP6" s="12"/>
-      <c r="CQ6" s="12"/>
-      <c r="CR6" s="12"/>
-      <c r="CS6" s="12"/>
-      <c r="CT6" s="12"/>
-      <c r="CU6" s="12"/>
-      <c r="CV6" s="12"/>
-      <c r="CW6" s="12"/>
-      <c r="CX6" s="12"/>
-      <c r="CY6" s="12"/>
-      <c r="CZ6" s="12"/>
-      <c r="DA6" s="12"/>
-      <c r="DB6" s="12"/>
-      <c r="DC6" s="12"/>
-      <c r="DD6" s="12"/>
-      <c r="DE6" s="12"/>
-      <c r="DF6" s="12"/>
-      <c r="DG6" s="12"/>
-      <c r="DH6" s="12"/>
-      <c r="DI6" s="12"/>
-      <c r="DJ6" s="12"/>
-      <c r="DK6" s="12"/>
-      <c r="DL6" s="12"/>
-      <c r="DM6" s="12"/>
-      <c r="DN6" s="12"/>
-      <c r="DO6" s="12"/>
-      <c r="DP6" s="12"/>
-      <c r="DQ6" s="12"/>
-      <c r="DR6" s="12"/>
-      <c r="DS6" s="12"/>
-      <c r="DT6" s="12"/>
-      <c r="DU6" s="12"/>
-      <c r="DV6" s="12"/>
-      <c r="DW6" s="12"/>
-      <c r="DX6" s="12"/>
-      <c r="DY6" s="12"/>
-      <c r="DZ6" s="12"/>
-      <c r="EA6" s="12"/>
-      <c r="EB6" s="12"/>
-      <c r="EC6" s="12"/>
-      <c r="ED6" s="12"/>
-      <c r="EE6" s="12"/>
-      <c r="EF6" s="12"/>
-      <c r="EG6" s="12"/>
-      <c r="EH6" s="12"/>
-      <c r="EI6" s="12"/>
-      <c r="EJ6" s="12"/>
-      <c r="EK6" s="12"/>
-      <c r="EL6" s="12"/>
-      <c r="EM6" s="12"/>
-      <c r="EN6" s="12"/>
-      <c r="EO6" s="12"/>
-      <c r="EP6" s="12"/>
-      <c r="EQ6" s="12"/>
-      <c r="ER6" s="12"/>
-      <c r="ES6" s="12"/>
-      <c r="ET6" s="12"/>
-      <c r="EU6" s="12"/>
-      <c r="EV6" s="12"/>
-      <c r="EW6" s="12"/>
-      <c r="EX6" s="12"/>
-      <c r="EY6" s="12"/>
-      <c r="EZ6" s="12"/>
-      <c r="FA6" s="12"/>
-      <c r="FB6" s="12"/>
-      <c r="FC6" s="12"/>
-      <c r="FD6" s="12"/>
-      <c r="FE6" s="12"/>
-      <c r="FF6" s="12"/>
-      <c r="FG6" s="12"/>
-      <c r="FH6" s="12"/>
-      <c r="FI6" s="12"/>
-      <c r="FJ6" s="12"/>
-      <c r="FK6" s="12"/>
-      <c r="FL6" s="12"/>
-      <c r="FM6" s="12"/>
-      <c r="FN6" s="12"/>
-      <c r="FO6" s="12"/>
-      <c r="FP6" s="12"/>
-      <c r="FQ6" s="12"/>
-      <c r="FR6" s="12"/>
-      <c r="FS6" s="12"/>
-      <c r="FT6" s="12"/>
-      <c r="FU6" s="12"/>
-      <c r="FV6" s="12"/>
-      <c r="FW6" s="12"/>
-      <c r="FX6" s="12"/>
-      <c r="FY6" s="12"/>
-      <c r="FZ6" s="12"/>
-      <c r="GA6" s="12"/>
-      <c r="GB6" s="12"/>
-      <c r="GC6" s="12"/>
-      <c r="GD6" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="GE6" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="GF6" s="12"/>
-      <c r="GG6" s="12"/>
-      <c r="GH6" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="GI6" s="3"/>
-      <c r="GJ6" s="3"/>
-      <c r="GK6" s="3"/>
-      <c r="GL6" s="3"/>
-      <c r="GM6" s="3"/>
-      <c r="GN6" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="GO6" s="12"/>
-      <c r="GP6" s="12"/>
-      <c r="GQ6" s="12"/>
-      <c r="GR6" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="GS6" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="GT6" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="GU6" s="12"/>
-      <c r="GV6" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="BH2:BY2"/>
+    <mergeCell ref="GF2:HB2"/>
+    <mergeCell ref="ET2:FK2"/>
     <mergeCell ref="GD2:GE2"/>
-    <mergeCell ref="GF2:HB2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="AP2:BG2"/>
+    <mergeCell ref="DJ2:EA2"/>
+    <mergeCell ref="F2:W2"/>
+    <mergeCell ref="EB2:ES2"/>
+    <mergeCell ref="FL2:GC2"/>
+    <mergeCell ref="A2:E2"/>
     <mergeCell ref="F1:GC1"/>
+    <mergeCell ref="X2:AO2"/>
     <mergeCell ref="GD1:GE1"/>
+    <mergeCell ref="BZ2:CQ2"/>
     <mergeCell ref="GF1:HB1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="F2:W2"/>
-    <mergeCell ref="X2:AO2"/>
-    <mergeCell ref="AP2:BG2"/>
-    <mergeCell ref="BH2:BY2"/>
-    <mergeCell ref="BZ2:CQ2"/>
     <mergeCell ref="CR2:DI2"/>
-    <mergeCell ref="DJ2:EA2"/>
-    <mergeCell ref="EB2:ES2"/>
-    <mergeCell ref="ET2:FK2"/>
-    <mergeCell ref="FL2:GC2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing r:id="rId1"/>
@@ -7310,157 +6560,157 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:BB14"/>
+  <dimension ref="A1:BB3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.1640625" customWidth="1"/>
-    <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="11.83203125" customWidth="1"/>
-    <col min="4" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="31.33203125" customWidth="1"/>
-    <col min="7" max="12" width="11.33203125" customWidth="1"/>
-    <col min="13" max="14" width="11.33203125" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="11" hidden="1" customWidth="1"/>
-    <col min="16" max="18" width="13.6640625" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="11.33203125" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="16.1640625" customWidth="1"/>
-    <col min="21" max="21" width="18" customWidth="1"/>
-    <col min="22" max="22" width="11" customWidth="1"/>
-    <col min="23" max="23" width="16.1640625" customWidth="1"/>
-    <col min="24" max="24" width="16.6640625" customWidth="1"/>
-    <col min="25" max="25" width="16.1640625" customWidth="1"/>
-    <col min="27" max="27" width="15.33203125" customWidth="1"/>
-    <col min="28" max="29" width="16.1640625" customWidth="1"/>
-    <col min="30" max="30" width="17" customWidth="1"/>
-    <col min="31" max="31" width="21.33203125" customWidth="1"/>
-    <col min="32" max="32" width="8.6640625" customWidth="1"/>
-    <col min="33" max="33" width="11" customWidth="1"/>
-    <col min="34" max="34" width="26.6640625" customWidth="1"/>
-    <col min="35" max="35" width="10.5" customWidth="1"/>
-    <col min="36" max="36" width="13.6640625" customWidth="1"/>
-    <col min="37" max="41" width="11" customWidth="1"/>
-    <col min="42" max="42" width="16.1640625" customWidth="1"/>
-    <col min="43" max="43" width="9.6640625" customWidth="1"/>
-    <col min="44" max="45" width="16.1640625" customWidth="1"/>
-    <col min="46" max="46" width="24" customWidth="1"/>
-    <col min="47" max="47" width="11" customWidth="1"/>
-    <col min="48" max="48" width="19.6640625" customWidth="1"/>
-    <col min="49" max="49" width="10.33203125" customWidth="1"/>
-    <col min="50" max="50" width="6" customWidth="1"/>
-    <col min="51" max="51" width="10.33203125" customWidth="1"/>
+    <col min="1" max="1" width="16.1640625" style="18" customWidth="1"/>
+    <col min="2" max="2" width="17" style="18" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" style="18" customWidth="1"/>
+    <col min="4" max="5" width="17" style="18" customWidth="1"/>
+    <col min="6" max="6" width="31.33203125" style="18" customWidth="1"/>
+    <col min="7" max="12" width="11.33203125" style="18" customWidth="1"/>
+    <col min="13" max="14" width="11.33203125" style="18" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="11" style="18" hidden="1" customWidth="1"/>
+    <col min="16" max="18" width="13.6640625" style="18" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="11.33203125" style="18" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="16.1640625" style="18" customWidth="1"/>
+    <col min="21" max="21" width="18" style="18" customWidth="1"/>
+    <col min="22" max="22" width="11" style="18" customWidth="1"/>
+    <col min="23" max="23" width="16.1640625" style="18" customWidth="1"/>
+    <col min="24" max="24" width="16.6640625" style="18" customWidth="1"/>
+    <col min="25" max="25" width="16.1640625" style="18" customWidth="1"/>
+    <col min="27" max="27" width="15.33203125" style="18" customWidth="1"/>
+    <col min="28" max="29" width="16.1640625" style="18" customWidth="1"/>
+    <col min="30" max="30" width="17" style="18" customWidth="1"/>
+    <col min="31" max="31" width="21.33203125" style="18" customWidth="1"/>
+    <col min="32" max="32" width="8.6640625" style="18" customWidth="1"/>
+    <col min="33" max="33" width="11" style="18" customWidth="1"/>
+    <col min="34" max="34" width="26.6640625" style="18" customWidth="1"/>
+    <col min="35" max="35" width="10.5" style="18" customWidth="1"/>
+    <col min="36" max="36" width="13.6640625" style="18" customWidth="1"/>
+    <col min="37" max="41" width="11" style="18" customWidth="1"/>
+    <col min="42" max="42" width="16.1640625" style="18" customWidth="1"/>
+    <col min="43" max="43" width="9.6640625" style="18" customWidth="1"/>
+    <col min="44" max="45" width="16.1640625" style="18" customWidth="1"/>
+    <col min="46" max="46" width="24" style="18" customWidth="1"/>
+    <col min="47" max="47" width="11" style="18" customWidth="1"/>
+    <col min="48" max="48" width="19.6640625" style="18" customWidth="1"/>
+    <col min="49" max="49" width="10.33203125" style="18" customWidth="1"/>
+    <col min="50" max="50" width="6" style="18" customWidth="1"/>
+    <col min="51" max="51" width="10.33203125" style="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="133" customHeight="1">
-      <c r="A1" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="40" t="s">
-        <v>92</v>
-      </c>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="41"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="38" t="s">
-        <v>93</v>
-      </c>
-      <c r="U1" s="39"/>
-      <c r="V1" s="39"/>
-      <c r="W1" s="39"/>
-      <c r="X1" s="40" t="s">
-        <v>94</v>
-      </c>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="41"/>
-      <c r="AA1" s="41"/>
-      <c r="AB1" s="41"/>
-      <c r="AC1" s="42"/>
-      <c r="AD1" s="38" t="s">
+      <c r="A1" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="21"/>
+      <c r="T1" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="21"/>
+      <c r="X1" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y1" s="20"/>
+      <c r="Z1" s="20"/>
+      <c r="AA1" s="20"/>
+      <c r="AB1" s="20"/>
+      <c r="AC1" s="21"/>
+      <c r="AD1" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="AE1" s="39"/>
-      <c r="AF1" s="26" t="s">
+      <c r="AE1" s="21"/>
+      <c r="AF1" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="AG1" s="26"/>
-      <c r="AH1" s="26"/>
-      <c r="AI1" s="26"/>
-      <c r="AJ1" s="26"/>
-      <c r="AK1" s="26"/>
-      <c r="AL1" s="26"/>
-      <c r="AM1" s="26"/>
-      <c r="AN1" s="26"/>
-      <c r="AO1" s="26"/>
-      <c r="AP1" s="26"/>
-      <c r="AQ1" s="26"/>
-      <c r="AR1" s="26"/>
-      <c r="AS1" s="26"/>
-      <c r="AT1" s="26"/>
-      <c r="AU1" s="26"/>
-      <c r="AV1" s="26"/>
-      <c r="AW1" s="26"/>
-      <c r="AX1" s="26"/>
-      <c r="AY1" s="26"/>
-      <c r="AZ1" s="26"/>
-      <c r="BA1" s="26"/>
-      <c r="BB1" s="26"/>
+      <c r="AG1" s="20"/>
+      <c r="AH1" s="20"/>
+      <c r="AI1" s="20"/>
+      <c r="AJ1" s="20"/>
+      <c r="AK1" s="20"/>
+      <c r="AL1" s="20"/>
+      <c r="AM1" s="20"/>
+      <c r="AN1" s="20"/>
+      <c r="AO1" s="20"/>
+      <c r="AP1" s="20"/>
+      <c r="AQ1" s="20"/>
+      <c r="AR1" s="20"/>
+      <c r="AS1" s="20"/>
+      <c r="AT1" s="20"/>
+      <c r="AU1" s="20"/>
+      <c r="AV1" s="20"/>
+      <c r="AW1" s="20"/>
+      <c r="AX1" s="20"/>
+      <c r="AY1" s="20"/>
+      <c r="AZ1" s="20"/>
+      <c r="BA1" s="20"/>
+      <c r="BB1" s="21"/>
     </row>
     <row r="2" spans="1:54" ht="18.25" customHeight="1">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
       <c r="D2" s="20"/>
       <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="29"/>
-      <c r="S2" s="36"/>
-      <c r="T2" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="U2" s="37"/>
-      <c r="V2" s="37"/>
-      <c r="W2" s="37"/>
-      <c r="X2" s="20" t="s">
-        <v>97</v>
+      <c r="F2" s="21"/>
+      <c r="G2" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="21"/>
+      <c r="T2" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="U2" s="20"/>
+      <c r="V2" s="20"/>
+      <c r="W2" s="21"/>
+      <c r="X2" s="27" t="s">
+        <v>81</v>
       </c>
       <c r="Y2" s="20"/>
       <c r="Z2" s="20"/>
       <c r="AA2" s="20"/>
       <c r="AB2" s="20"/>
-      <c r="AC2" s="20"/>
-      <c r="AD2" s="20" t="s">
+      <c r="AC2" s="21"/>
+      <c r="AD2" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="AE2" s="20"/>
-      <c r="AF2" s="20" t="s">
+      <c r="AE2" s="21"/>
+      <c r="AF2" s="27" t="s">
         <v>17</v>
       </c>
       <c r="AG2" s="20"/>
@@ -7484,9 +6734,9 @@
       <c r="AY2" s="20"/>
       <c r="AZ2" s="20"/>
       <c r="BA2" s="20"/>
-      <c r="BB2" s="20"/>
+      <c r="BB2" s="21"/>
     </row>
-    <row r="3" spans="1:54" ht="17">
+    <row r="3" spans="1:54" ht="17" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>18</v>
       </c>
@@ -7503,7 +6753,7 @@
         <v>22</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>25</v>
@@ -7545,34 +6795,34 @@
         <v>37</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="U3" s="10" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="V3" s="9" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="W3" s="9" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="X3" s="11" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="Y3" s="9" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="Z3" s="9" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="AA3" s="9" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="AB3" s="9" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="AC3" s="9" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="AD3" s="6" t="s">
         <v>16</v>
@@ -7649,965 +6899,21 @@
       <c r="BB3" s="14" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="4" spans="1:54" ht="16">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3">
-        <v>69</v>
-      </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="U4" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="V4" s="3"/>
-      <c r="W4" s="3"/>
-      <c r="X4" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y4" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z4" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="12"/>
-      <c r="AB4" s="12"/>
-      <c r="AC4" s="12"/>
-      <c r="AD4" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="AE4" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="AF4" s="12"/>
-      <c r="AG4" s="12"/>
-      <c r="AH4" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="AI4" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ4" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="AK4" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="AL4" s="3"/>
-      <c r="AM4" s="3"/>
-      <c r="AN4" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="AO4" s="12"/>
-      <c r="AP4" s="12"/>
-      <c r="AQ4" s="12"/>
-      <c r="AR4" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="AS4" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="AT4" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="AU4" s="12"/>
-      <c r="AV4" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="AW4" s="4"/>
-      <c r="AX4" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="AY4" s="4"/>
-      <c r="AZ4" s="4"/>
-      <c r="BA4" s="4"/>
-      <c r="BB4" s="4"/>
-    </row>
-    <row r="5" spans="1:54" ht="16">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3">
-        <v>69</v>
-      </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="U5" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="V5" s="3"/>
-      <c r="W5" s="3"/>
-      <c r="X5" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="Y5" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z5" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="12"/>
-      <c r="AB5" s="12"/>
-      <c r="AC5" s="12"/>
-      <c r="AD5" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE5" s="12"/>
-      <c r="AF5" s="12"/>
-      <c r="AG5" s="12"/>
-      <c r="AH5" s="3"/>
-      <c r="AI5" s="3"/>
-      <c r="AJ5" s="3"/>
-      <c r="AK5" s="3"/>
-      <c r="AL5" s="3"/>
-      <c r="AM5" s="3"/>
-      <c r="AN5" s="3"/>
-      <c r="AO5" s="12"/>
-      <c r="AP5" s="12"/>
-      <c r="AQ5" s="12"/>
-      <c r="AR5" s="12"/>
-      <c r="AS5" s="12"/>
-      <c r="AT5" s="12"/>
-      <c r="AU5" s="12"/>
-      <c r="AV5" s="12"/>
-      <c r="AW5" s="4"/>
-      <c r="AX5" s="4"/>
-      <c r="AY5" s="4"/>
-      <c r="AZ5" s="4"/>
-      <c r="BA5" s="4"/>
-      <c r="BB5" s="4"/>
-    </row>
-    <row r="6" spans="1:54" ht="16">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3">
-        <v>69</v>
-      </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="U6" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="V6" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="W6" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="X6" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="Y6" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z6" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="AB6" s="12"/>
-      <c r="AC6" s="12"/>
-      <c r="AD6" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE6" s="12"/>
-      <c r="AF6" s="12"/>
-      <c r="AG6" s="12"/>
-      <c r="AH6" s="3"/>
-      <c r="AI6" s="3"/>
-      <c r="AJ6" s="3"/>
-      <c r="AK6" s="3"/>
-      <c r="AL6" s="3"/>
-      <c r="AM6" s="3"/>
-      <c r="AN6" s="3"/>
-      <c r="AO6" s="12"/>
-      <c r="AP6" s="12"/>
-      <c r="AQ6" s="12"/>
-      <c r="AR6" s="12"/>
-      <c r="AS6" s="12"/>
-      <c r="AT6" s="12"/>
-      <c r="AU6" s="12"/>
-      <c r="AV6" s="12"/>
-      <c r="AW6" s="4"/>
-      <c r="AX6" s="4"/>
-      <c r="AY6" s="4"/>
-      <c r="AZ6" s="4"/>
-      <c r="BA6" s="4"/>
-      <c r="BB6" s="4"/>
-    </row>
-    <row r="7" spans="1:54" ht="16">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3">
-        <v>69</v>
-      </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="U7" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="V7" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="W7" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="X7" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="Y7" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z7" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB7" s="12"/>
-      <c r="AC7" s="12"/>
-      <c r="AD7" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE7" s="12"/>
-      <c r="AF7" s="12"/>
-      <c r="AG7" s="12"/>
-      <c r="AH7" s="12"/>
-      <c r="AI7" s="12"/>
-      <c r="AJ7" s="12"/>
-      <c r="AK7" s="12"/>
-      <c r="AL7" s="12"/>
-      <c r="AM7" s="12"/>
-      <c r="AN7" s="3"/>
-      <c r="AO7" s="12"/>
-      <c r="AP7" s="3"/>
-      <c r="AQ7" s="3"/>
-      <c r="AR7" s="3"/>
-      <c r="AS7" s="3"/>
-      <c r="AT7" s="3"/>
-      <c r="AU7" s="4"/>
-      <c r="AV7" s="4"/>
-      <c r="AW7" s="4"/>
-      <c r="AX7" s="4"/>
-      <c r="AY7" s="4"/>
-      <c r="AZ7" s="4"/>
-      <c r="BA7" s="4"/>
-      <c r="BB7" s="4"/>
-    </row>
-    <row r="8" spans="1:54" ht="16">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3">
-        <v>69</v>
-      </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="V8" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="W8" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="X8" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y8" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z8" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="AB8" s="12"/>
-      <c r="AC8" s="12"/>
-      <c r="AD8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE8" s="12"/>
-      <c r="AF8" s="12"/>
-      <c r="AG8" s="12"/>
-      <c r="AH8" s="12"/>
-      <c r="AI8" s="12"/>
-      <c r="AJ8" s="12"/>
-      <c r="AK8" s="12"/>
-      <c r="AL8" s="12"/>
-      <c r="AM8" s="12"/>
-      <c r="AN8" s="3"/>
-      <c r="AO8" s="12"/>
-      <c r="AP8" s="3"/>
-      <c r="AQ8" s="3"/>
-      <c r="AR8" s="3"/>
-      <c r="AS8" s="3"/>
-      <c r="AT8" s="3"/>
-      <c r="AU8" s="4"/>
-      <c r="AV8" s="4"/>
-      <c r="AW8" s="4"/>
-      <c r="AX8" s="4"/>
-      <c r="AY8" s="4"/>
-      <c r="AZ8" s="4"/>
-      <c r="BA8" s="4"/>
-      <c r="BB8" s="4"/>
-    </row>
-    <row r="9" spans="1:54" ht="16">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3">
-        <v>69</v>
-      </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y9" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="Z9" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="12"/>
-      <c r="AB9" s="12">
-        <v>2</v>
-      </c>
-      <c r="AC9" s="12"/>
-      <c r="AD9" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE9" s="12"/>
-      <c r="AF9" s="12"/>
-      <c r="AG9" s="12"/>
-      <c r="AH9" s="12"/>
-      <c r="AI9" s="12"/>
-      <c r="AJ9" s="12"/>
-      <c r="AK9" s="12"/>
-      <c r="AL9" s="12"/>
-      <c r="AM9" s="12"/>
-      <c r="AN9" s="3"/>
-      <c r="AO9" s="12"/>
-      <c r="AP9" s="3"/>
-      <c r="AQ9" s="3"/>
-      <c r="AR9" s="3"/>
-      <c r="AS9" s="3"/>
-      <c r="AT9" s="3"/>
-      <c r="AU9" s="4"/>
-      <c r="AV9" s="4"/>
-      <c r="AW9" s="4"/>
-      <c r="AX9" s="4"/>
-      <c r="AY9" s="4"/>
-      <c r="AZ9" s="4"/>
-      <c r="BA9" s="4"/>
-      <c r="BB9" s="4"/>
-    </row>
-    <row r="10" spans="1:54" ht="16">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3">
-        <v>69</v>
-      </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="U10" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
-      <c r="X10" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="Y10" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="Z10" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="12"/>
-      <c r="AB10" s="12">
-        <v>2</v>
-      </c>
-      <c r="AC10" s="12"/>
-      <c r="AD10" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE10" s="12"/>
-      <c r="AF10" s="12"/>
-      <c r="AG10" s="12"/>
-      <c r="AH10" s="12"/>
-      <c r="AI10" s="12"/>
-      <c r="AJ10" s="12"/>
-      <c r="AK10" s="12"/>
-      <c r="AL10" s="12"/>
-      <c r="AM10" s="12"/>
-      <c r="AN10" s="3"/>
-      <c r="AO10" s="12"/>
-      <c r="AP10" s="3"/>
-      <c r="AQ10" s="3"/>
-      <c r="AR10" s="3"/>
-      <c r="AS10" s="3"/>
-      <c r="AT10" s="3"/>
-      <c r="AU10" s="4"/>
-      <c r="AV10" s="4"/>
-      <c r="AW10" s="4"/>
-      <c r="AX10" s="4"/>
-      <c r="AY10" s="4"/>
-      <c r="AZ10" s="4"/>
-      <c r="BA10" s="4"/>
-      <c r="BB10" s="4"/>
-    </row>
-    <row r="11" spans="1:54" ht="16">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3">
-        <v>39</v>
-      </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="U11" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
-      <c r="X11" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y11" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z11" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="12"/>
-      <c r="AB11" s="12"/>
-      <c r="AC11" s="12">
-        <v>19</v>
-      </c>
-      <c r="AD11" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="AE11" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="AF11" s="12"/>
-      <c r="AG11" s="12"/>
-      <c r="AH11" s="12"/>
-      <c r="AI11" s="12"/>
-      <c r="AJ11" s="12"/>
-      <c r="AK11" s="12"/>
-      <c r="AL11" s="12"/>
-      <c r="AM11" s="12"/>
-      <c r="AN11" s="3"/>
-      <c r="AO11" s="12"/>
-      <c r="AP11" s="3"/>
-      <c r="AQ11" s="3"/>
-      <c r="AR11" s="3"/>
-      <c r="AS11" s="3"/>
-      <c r="AT11" s="3"/>
-      <c r="AU11" s="4"/>
-      <c r="AV11" s="4"/>
-      <c r="AW11" s="4"/>
-      <c r="AX11" s="4"/>
-      <c r="AY11" s="4"/>
-      <c r="AZ11" s="4"/>
-      <c r="BA11" s="4"/>
-      <c r="BB11" s="4"/>
-    </row>
-    <row r="12" spans="1:54" ht="16">
-      <c r="A12" s="4"/>
-      <c r="B12" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3">
-        <v>39</v>
-      </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="U12" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="V12" s="3"/>
-      <c r="W12" s="3"/>
-      <c r="X12" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y12" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z12" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="4"/>
-      <c r="AB12" s="4"/>
-      <c r="AC12" s="4">
-        <v>9</v>
-      </c>
-      <c r="AD12" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE12" s="4"/>
-      <c r="AF12" s="4"/>
-      <c r="AG12" s="4"/>
-      <c r="AH12" s="4"/>
-      <c r="AI12" s="4"/>
-      <c r="AJ12" s="4"/>
-      <c r="AK12" s="4"/>
-      <c r="AL12" s="4"/>
-      <c r="AM12" s="4"/>
-      <c r="AN12" s="4"/>
-      <c r="AO12" s="4"/>
-      <c r="AP12" s="4"/>
-      <c r="AQ12" s="4"/>
-      <c r="AR12" s="4"/>
-      <c r="AS12" s="4"/>
-      <c r="AT12" s="4"/>
-      <c r="AU12" s="4"/>
-      <c r="AV12" s="4"/>
-      <c r="AW12" s="4"/>
-      <c r="AX12" s="4"/>
-      <c r="AY12" s="4"/>
-      <c r="AZ12" s="4"/>
-      <c r="BA12" s="4"/>
-      <c r="BB12" s="4"/>
-    </row>
-    <row r="13" spans="1:54" ht="16">
-      <c r="A13" s="4"/>
-      <c r="B13" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3">
-        <v>39</v>
-      </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="U13" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="V13" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="W13" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="X13" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="Y13" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z13" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA13" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB13" s="4"/>
-      <c r="AC13" s="4">
-        <v>1</v>
-      </c>
-      <c r="AD13" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE13" s="4"/>
-      <c r="AF13" s="4"/>
-      <c r="AG13" s="4"/>
-      <c r="AH13" s="4"/>
-      <c r="AI13" s="4"/>
-      <c r="AJ13" s="4"/>
-      <c r="AK13" s="4"/>
-      <c r="AL13" s="4"/>
-      <c r="AM13" s="4"/>
-      <c r="AN13" s="4"/>
-      <c r="AO13" s="4"/>
-      <c r="AP13" s="4"/>
-      <c r="AQ13" s="4"/>
-      <c r="AR13" s="4"/>
-      <c r="AS13" s="4"/>
-      <c r="AT13" s="4"/>
-      <c r="AU13" s="4"/>
-      <c r="AV13" s="4"/>
-      <c r="AW13" s="4"/>
-      <c r="AX13" s="4"/>
-      <c r="AY13" s="4"/>
-      <c r="AZ13" s="4"/>
-      <c r="BA13" s="4"/>
-      <c r="BB13" s="4"/>
-    </row>
-    <row r="14" spans="1:54" ht="16">
-      <c r="A14" s="4"/>
-      <c r="B14" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3">
-        <v>39</v>
-      </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
-      <c r="T14" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="V14" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="X14" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="Y14" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z14" s="12">
-        <v>1</v>
-      </c>
-      <c r="AA14" s="4"/>
-      <c r="AB14" s="4"/>
-      <c r="AC14" s="4">
-        <v>1</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE14" s="4"/>
-      <c r="AF14" s="4"/>
-      <c r="AG14" s="4"/>
-      <c r="AH14" s="4"/>
-      <c r="AI14" s="4"/>
-      <c r="AJ14" s="4"/>
-      <c r="AK14" s="4"/>
-      <c r="AL14" s="4"/>
-      <c r="AM14" s="4"/>
-      <c r="AN14" s="4"/>
-      <c r="AO14" s="4"/>
-      <c r="AP14" s="4"/>
-      <c r="AQ14" s="4"/>
-      <c r="AR14" s="4"/>
-      <c r="AS14" s="4"/>
-      <c r="AT14" s="4"/>
-      <c r="AU14" s="4"/>
-      <c r="AV14" s="4"/>
-      <c r="AW14" s="4"/>
-      <c r="AX14" s="4"/>
-      <c r="AY14" s="4"/>
-      <c r="AZ14" s="4"/>
-      <c r="BA14" s="4"/>
-      <c r="BB14" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="AF1:BB1"/>
+    <mergeCell ref="X2:AC2"/>
+    <mergeCell ref="G1:S1"/>
+    <mergeCell ref="AF2:BB2"/>
+    <mergeCell ref="T1:W1"/>
+    <mergeCell ref="G2:S2"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:S2"/>
-    <mergeCell ref="T2:W2"/>
-    <mergeCell ref="X2:AC2"/>
-    <mergeCell ref="AD2:AE2"/>
-    <mergeCell ref="AF2:BB2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:S1"/>
-    <mergeCell ref="T1:W1"/>
     <mergeCell ref="X1:AC1"/>
     <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="AD2:AE2"/>
+    <mergeCell ref="T2:W2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing r:id="rId1"/>
